--- a/Images_BGA/Results/Reports/PCBA2_06_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_06_inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="29">
   <si>
     <t>image_name</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>total_balls</t>
@@ -588,31 +591,31 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1846</v>
+        <v>1835</v>
       </c>
       <c r="D4">
         <v>1205</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F4">
-        <v>1385.44</v>
+        <v>1963.5</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="I4">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="J4">
-        <v>3.8977</v>
+        <v>6.7736</v>
       </c>
       <c r="K4">
-        <v>3.8977</v>
+        <v>3.7179</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -679,13 +682,13 @@
         <v>1117</v>
       </c>
       <c r="D6">
-        <v>1210</v>
+        <v>1202</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -852,31 +855,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D10">
         <v>1210</v>
       </c>
       <c r="E10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>1661.9</v>
+        <v>1520.53</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J10">
-        <v>1.9857</v>
+        <v>2.6307</v>
       </c>
       <c r="K10">
-        <v>1.0229</v>
+        <v>1.5784</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -984,31 +987,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="D13">
-        <v>1210</v>
+        <v>1201</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F13">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J13">
-        <v>1.7316</v>
+        <v>1.4126</v>
       </c>
       <c r="K13">
-        <v>1.7316</v>
+        <v>1.4126</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1116,7 +1119,7 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D16">
         <v>1212</v>
@@ -1128,16 +1131,16 @@
         <v>1809.56</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I16">
         <v>39</v>
       </c>
       <c r="J16">
-        <v>2.1552</v>
+        <v>3.0394</v>
       </c>
       <c r="K16">
         <v>2.1552</v>
@@ -1248,31 +1251,31 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>1958</v>
+        <v>1945</v>
       </c>
       <c r="D19">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E19">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F19">
-        <v>1385.44</v>
+        <v>1134.11</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>9.5228</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1292,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D20">
         <v>1259</v>
@@ -1307,16 +1310,16 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I20">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J20">
-        <v>2.5272</v>
+        <v>2.4671</v>
       </c>
       <c r="K20">
-        <v>2.5272</v>
+        <v>2.4671</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1380,31 +1383,31 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="D22">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F22">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>0.8149</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>0.8149</v>
+        <v>0</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1424,16 +1427,16 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D23">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F23">
-        <v>1661.9</v>
+        <v>1520.53</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1445,10 +1448,10 @@
         <v>55</v>
       </c>
       <c r="J23">
-        <v>3.3095</v>
+        <v>3.6172</v>
       </c>
       <c r="K23">
-        <v>3.3095</v>
+        <v>3.6172</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1468,31 +1471,31 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="D24">
-        <v>1260</v>
+        <v>1295</v>
       </c>
       <c r="E24">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F24">
-        <v>1661.9</v>
+        <v>1134.11</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1.6848</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>1.6848</v>
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1512,16 +1515,16 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="D25">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="E25">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F25">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1556,16 +1559,16 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="D26">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="E26">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F26">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1600,16 +1603,16 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1195</v>
+        <v>1182</v>
       </c>
       <c r="D27">
         <v>1260</v>
       </c>
       <c r="E27">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F27">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1776,31 +1779,31 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="D31">
-        <v>1260</v>
+        <v>1297</v>
       </c>
       <c r="E31">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F31">
-        <v>1385.44</v>
+        <v>1134.11</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1.6601</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1.6601</v>
+        <v>0</v>
       </c>
       <c r="L31" t="s">
         <v>15</v>
@@ -1864,16 +1867,16 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D33">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E33">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F33">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1952,16 +1955,16 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="D35">
         <v>1309</v>
       </c>
       <c r="E35">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F35">
-        <v>1661.9</v>
+        <v>1520.53</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2040,16 +2043,16 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="D37">
         <v>1309</v>
       </c>
       <c r="E37">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F37">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -2128,16 +2131,16 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1835</v>
+        <v>1827</v>
       </c>
       <c r="D39">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E39">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F39">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2172,16 +2175,16 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="D40">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E40">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F40">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2193,10 +2196,10 @@
         <v>28</v>
       </c>
       <c r="J40">
-        <v>1.5473</v>
+        <v>1.3184</v>
       </c>
       <c r="K40">
-        <v>1.5473</v>
+        <v>1.3184</v>
       </c>
       <c r="L40" t="s">
         <v>15</v>
@@ -2216,16 +2219,16 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="D41">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E41">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F41">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2260,10 +2263,10 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="D42">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E42">
         <v>46</v>
@@ -2304,31 +2307,31 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="D43">
-        <v>1310</v>
+        <v>1345</v>
       </c>
       <c r="E43">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F43">
-        <v>1661.9</v>
+        <v>1134.11</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>3.2625</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1.8517</v>
       </c>
       <c r="L43" t="s">
         <v>15</v>
@@ -2348,31 +2351,31 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="D44">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="E44">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F44">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>2.7077</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>1.5645</v>
+        <v>0</v>
       </c>
       <c r="L44" t="s">
         <v>15</v>
@@ -2439,13 +2442,13 @@
         <v>1195</v>
       </c>
       <c r="D46">
-        <v>1310</v>
+        <v>1347</v>
       </c>
       <c r="E46">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F46">
-        <v>1661.9</v>
+        <v>1134.11</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2480,7 +2483,7 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D47">
         <v>1310</v>
@@ -2568,34 +2571,34 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>1954</v>
+        <v>1938</v>
       </c>
       <c r="D49">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E49">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F49">
-        <v>1661.9</v>
+        <v>1520.53</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>13.5479</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>13.5479</v>
       </c>
       <c r="L49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -2612,31 +2615,31 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="D50">
         <v>1358</v>
       </c>
       <c r="E50">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F50">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="I50">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J50">
-        <v>3.7688</v>
+        <v>2.5421</v>
       </c>
       <c r="K50">
-        <v>1.5788</v>
+        <v>1.3263</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2656,31 +2659,31 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>1920</v>
+        <v>1927</v>
       </c>
       <c r="D51">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="E51">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F51">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I51">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J51">
-        <v>1.0695</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K51">
-        <v>1.0695</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2700,31 +2703,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="D52">
         <v>1359</v>
       </c>
       <c r="E52">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F52">
-        <v>1809.56</v>
+        <v>1520.53</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1.1838</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1.1838</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2744,16 +2747,16 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="D53">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="E53">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F53">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2765,10 +2768,10 @@
         <v>37</v>
       </c>
       <c r="J53">
-        <v>2.9289</v>
+        <v>2.6993</v>
       </c>
       <c r="K53">
-        <v>2.0447</v>
+        <v>1.8844</v>
       </c>
       <c r="L53" t="s">
         <v>15</v>
@@ -2788,31 +2791,31 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D54">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E54">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F54">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I54">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J54">
-        <v>4.8078</v>
+        <v>5.4155</v>
       </c>
       <c r="K54">
-        <v>4.8078</v>
+        <v>5.4155</v>
       </c>
       <c r="L54" t="s">
         <v>15</v>
@@ -2835,7 +2838,7 @@
         <v>874</v>
       </c>
       <c r="D55">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E55">
         <v>48</v>
@@ -2876,31 +2879,31 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D56">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E56">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F56">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="I56">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J56">
-        <v>1.8237</v>
+        <v>3.3696</v>
       </c>
       <c r="K56">
-        <v>0.9395</v>
+        <v>1.2636</v>
       </c>
       <c r="L56" t="s">
         <v>15</v>
@@ -2964,31 +2967,31 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="D58">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="E58">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F58">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I58">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J58">
-        <v>2.7077</v>
+        <v>0.9677</v>
       </c>
       <c r="K58">
-        <v>1.5645</v>
+        <v>0.9677</v>
       </c>
       <c r="L58" t="s">
         <v>15</v>
@@ -3052,7 +3055,7 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D60">
         <v>1360</v>
@@ -3096,7 +3099,7 @@
         <v>60</v>
       </c>
       <c r="C61">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="D61">
         <v>1360</v>
@@ -3184,10 +3187,10 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="D63">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E63">
         <v>48</v>
@@ -3228,16 +3231,16 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="D64">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E64">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F64">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3272,31 +3275,31 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>1598</v>
+        <v>1594</v>
       </c>
       <c r="D65">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E65">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F65">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G65">
         <v>2</v>
       </c>
       <c r="H65">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I65">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J65">
-        <v>3.7179</v>
+        <v>3.8683</v>
       </c>
       <c r="K65">
-        <v>2.2409</v>
+        <v>2.2657</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3316,31 +3319,31 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>1953</v>
+        <v>1943</v>
       </c>
       <c r="D66">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F66">
-        <v>1520.53</v>
+        <v>2123.72</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="I66">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J66">
-        <v>10.5884</v>
+        <v>5.0383</v>
       </c>
       <c r="K66">
-        <v>5.2613</v>
+        <v>3.6257</v>
       </c>
       <c r="L66" t="s">
         <v>15</v>
@@ -3404,31 +3407,31 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="D68">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="E68">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F68">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I68">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J68">
-        <v>2.7078</v>
+        <v>1.7422</v>
       </c>
       <c r="K68">
-        <v>2.7078</v>
+        <v>1.7422</v>
       </c>
       <c r="L68" t="s">
         <v>15</v>
@@ -3495,28 +3498,28 @@
         <v>953</v>
       </c>
       <c r="D70">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E70">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F70">
-        <v>1809.56</v>
+        <v>1520.53</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I70">
         <v>36</v>
       </c>
       <c r="J70">
-        <v>4.0894</v>
+        <v>3.5514</v>
       </c>
       <c r="K70">
-        <v>1.9894</v>
+        <v>2.3676</v>
       </c>
       <c r="L70" t="s">
         <v>15</v>
@@ -3536,16 +3539,16 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="D71">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="E71">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F71">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3580,31 +3583,31 @@
         <v>71</v>
       </c>
       <c r="C72">
-        <v>1073</v>
+        <v>1109</v>
       </c>
       <c r="D72">
         <v>1411</v>
       </c>
       <c r="E72">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F72">
-        <v>2123.72</v>
+        <v>1134.11</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>2.2044</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>2.2044</v>
       </c>
       <c r="L72" t="s">
         <v>15</v>
@@ -3715,7 +3718,7 @@
         <v>1599</v>
       </c>
       <c r="D75">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E75">
         <v>48</v>
@@ -3756,16 +3759,16 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="D76">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="E76">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F76">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3777,10 +3780,10 @@
         <v>16</v>
       </c>
       <c r="J76">
-        <v>0.8842</v>
+        <v>0.7534</v>
       </c>
       <c r="K76">
-        <v>0.8842</v>
+        <v>0.7534</v>
       </c>
       <c r="L76" t="s">
         <v>15</v>
@@ -3800,10 +3803,10 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1844</v>
+        <v>1850</v>
       </c>
       <c r="D77">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="E77">
         <v>50</v>
@@ -3815,13 +3818,13 @@
         <v>2</v>
       </c>
       <c r="H77">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I77">
         <v>42</v>
       </c>
       <c r="J77">
-        <v>3.2086</v>
+        <v>3.1067</v>
       </c>
       <c r="K77">
         <v>2.139</v>
@@ -3844,10 +3847,10 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D78">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E78">
         <v>48</v>
@@ -3932,16 +3935,16 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="D80">
         <v>1412</v>
       </c>
       <c r="E80">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F80">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -3976,16 +3979,16 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="D81">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="E81">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F81">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -4020,31 +4023,31 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D82">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="E82">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F82">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I82">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J82">
-        <v>2.2409</v>
+        <v>2.4868</v>
       </c>
       <c r="K82">
-        <v>2.2409</v>
+        <v>2.4868</v>
       </c>
       <c r="L82" t="s">
         <v>15</v>
@@ -4067,28 +4070,28 @@
         <v>951</v>
       </c>
       <c r="D83">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E83">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F83">
-        <v>1809.56</v>
+        <v>1520.53</v>
       </c>
       <c r="G83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H83">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I83">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J83">
-        <v>2.7078</v>
+        <v>1.3153</v>
       </c>
       <c r="K83">
-        <v>1.6026</v>
+        <v>1.3153</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
@@ -4108,10 +4111,10 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="D84">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="E84">
         <v>52</v>
@@ -4152,16 +4155,16 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D85">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E85">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F85">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -4240,7 +4243,7 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="D87">
         <v>1463</v>
@@ -4372,31 +4375,31 @@
         <v>89</v>
       </c>
       <c r="C90">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D90">
         <v>1464</v>
       </c>
       <c r="E90">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F90">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G90">
         <v>1</v>
       </c>
       <c r="H90">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I90">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J90">
-        <v>1.9342</v>
+        <v>2.3467</v>
       </c>
       <c r="K90">
-        <v>1.9342</v>
+        <v>2.3467</v>
       </c>
       <c r="L90" t="s">
         <v>15</v>
@@ -4416,10 +4419,10 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="D91">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E91">
         <v>48</v>
@@ -4431,16 +4434,16 @@
         <v>1</v>
       </c>
       <c r="H91">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I91">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J91">
-        <v>0.9947</v>
+        <v>1.3263</v>
       </c>
       <c r="K91">
-        <v>0.9947</v>
+        <v>1.3263</v>
       </c>
       <c r="L91" t="s">
         <v>15</v>
@@ -4460,16 +4463,16 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="D92">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E92">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F92">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -4504,16 +4507,16 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D93">
         <v>1464</v>
       </c>
       <c r="E93">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F93">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -4551,28 +4554,28 @@
         <v>1358</v>
       </c>
       <c r="D94">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E94">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F94">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G94">
         <v>2</v>
       </c>
       <c r="H94">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I94">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J94">
-        <v>2.8521</v>
+        <v>2.4015</v>
       </c>
       <c r="K94">
-        <v>1.5279</v>
+        <v>1.2243</v>
       </c>
       <c r="L94" t="s">
         <v>15</v>
@@ -4592,10 +4595,10 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="D95">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E95">
         <v>50</v>
@@ -4636,10 +4639,10 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>1949</v>
+        <v>1943</v>
       </c>
       <c r="D96">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="E96">
         <v>52</v>
@@ -4680,7 +4683,7 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D97">
         <v>1470</v>
@@ -4768,10 +4771,10 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="D99">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="E99">
         <v>50</v>
@@ -4812,7 +4815,7 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="D100">
         <v>1515</v>
@@ -4827,16 +4830,16 @@
         <v>1</v>
       </c>
       <c r="H100">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I100">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J100">
-        <v>1.6579</v>
+        <v>1.8237</v>
       </c>
       <c r="K100">
-        <v>1.6579</v>
+        <v>1.8237</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -4856,16 +4859,16 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D101">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="E101">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F101">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -4877,10 +4880,10 @@
         <v>50</v>
       </c>
       <c r="J101">
-        <v>2.5465</v>
+        <v>2.7631</v>
       </c>
       <c r="K101">
-        <v>2.5465</v>
+        <v>2.7631</v>
       </c>
       <c r="L101" t="s">
         <v>15</v>
@@ -4900,16 +4903,16 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D102">
         <v>1516</v>
       </c>
       <c r="E102">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F102">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4944,7 +4947,7 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D103">
         <v>1516</v>
@@ -4988,31 +4991,31 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="D104">
         <v>1516</v>
       </c>
       <c r="E104">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F104">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G104">
         <v>1</v>
       </c>
       <c r="H104">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I104">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J104">
-        <v>1.1052</v>
+        <v>1.1433</v>
       </c>
       <c r="K104">
-        <v>1.1052</v>
+        <v>1.1433</v>
       </c>
       <c r="L104" t="s">
         <v>15</v>
@@ -5032,16 +5035,16 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>1853</v>
+        <v>1858</v>
       </c>
       <c r="D105">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="E105">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F105">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -5120,31 +5123,31 @@
         <v>106</v>
       </c>
       <c r="C107">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="D107">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F107">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H107">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="I107">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J107">
-        <v>3.3104</v>
+        <v>5.4621</v>
       </c>
       <c r="K107">
-        <v>1.8335</v>
+        <v>2.2602</v>
       </c>
       <c r="L107" t="s">
         <v>15</v>
@@ -5208,16 +5211,16 @@
         <v>108</v>
       </c>
       <c r="C109">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D109">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F109">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -5255,13 +5258,13 @@
         <v>1441</v>
       </c>
       <c r="D110">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="E110">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F110">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -5428,31 +5431,31 @@
         <v>113</v>
       </c>
       <c r="C114">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D114">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E114">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F114">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J114">
-        <v>1.0695</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>1.0695</v>
+        <v>0</v>
       </c>
       <c r="L114" t="s">
         <v>15</v>
@@ -5472,31 +5475,31 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="D115">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="E115">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F115">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G115">
         <v>1</v>
       </c>
       <c r="H115">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="I115">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="J115">
-        <v>6.3662</v>
+        <v>1.3655</v>
       </c>
       <c r="K115">
-        <v>6.3662</v>
+        <v>1.3655</v>
       </c>
       <c r="L115" t="s">
         <v>15</v>
@@ -5516,7 +5519,7 @@
         <v>115</v>
       </c>
       <c r="C116">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D116">
         <v>1569</v>
@@ -5560,10 +5563,10 @@
         <v>116</v>
       </c>
       <c r="C117">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="D117">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E117">
         <v>48</v>
@@ -5604,31 +5607,31 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D118">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E118">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F118">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="I118">
         <v>77</v>
       </c>
       <c r="J118">
-        <v>3.9216</v>
+        <v>5.1394</v>
       </c>
       <c r="K118">
-        <v>3.9216</v>
+        <v>4.2552</v>
       </c>
       <c r="L118" t="s">
         <v>15</v>
@@ -5692,16 +5695,16 @@
         <v>119</v>
       </c>
       <c r="C120">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D120">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E120">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F120">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -5713,10 +5716,10 @@
         <v>75</v>
       </c>
       <c r="J120">
-        <v>3.8197</v>
+        <v>4.1447</v>
       </c>
       <c r="K120">
-        <v>3.8197</v>
+        <v>4.1447</v>
       </c>
       <c r="L120" t="s">
         <v>15</v>
@@ -5868,10 +5871,10 @@
         <v>123</v>
       </c>
       <c r="C124">
-        <v>1858</v>
+        <v>1863</v>
       </c>
       <c r="D124">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="E124">
         <v>50</v>
@@ -5880,19 +5883,19 @@
         <v>1963.5</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I124">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J124">
-        <v>0.8149</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>0.8149</v>
+        <v>0</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5956,10 +5959,10 @@
         <v>125</v>
       </c>
       <c r="C126">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="D126">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="E126">
         <v>52</v>
@@ -5968,19 +5971,19 @@
         <v>2123.72</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I126">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J126">
-        <v>0</v>
+        <v>2.8723</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>2.8723</v>
       </c>
       <c r="L126" t="s">
         <v>15</v>
@@ -6088,10 +6091,10 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="D129">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="E129">
         <v>52</v>
@@ -6100,19 +6103,19 @@
         <v>2123.72</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>0.9888</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>0.9888</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -6132,16 +6135,16 @@
         <v>129</v>
       </c>
       <c r="C130">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D130">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="E130">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F130">
-        <v>1963.5</v>
+        <v>1520.53</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -6176,16 +6179,16 @@
         <v>130</v>
       </c>
       <c r="C131">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="D131">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="E131">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F131">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -6197,10 +6200,10 @@
         <v>16</v>
       </c>
       <c r="J131">
-        <v>0.7534</v>
+        <v>0.8149</v>
       </c>
       <c r="K131">
-        <v>0.7534</v>
+        <v>0.8149</v>
       </c>
       <c r="L131" t="s">
         <v>15</v>
@@ -6223,28 +6226,28 @@
         <v>1694</v>
       </c>
       <c r="D132">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="E132">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F132">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G132">
         <v>1</v>
       </c>
       <c r="H132">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I132">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J132">
-        <v>1.477</v>
+        <v>2.106</v>
       </c>
       <c r="K132">
-        <v>1.477</v>
+        <v>2.106</v>
       </c>
       <c r="L132" t="s">
         <v>15</v>
@@ -6264,7 +6267,7 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="D133">
         <v>1623</v>
@@ -6355,28 +6358,28 @@
         <v>1944</v>
       </c>
       <c r="D135">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="E135">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F135">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G135">
         <v>2</v>
       </c>
       <c r="H135">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I135">
         <v>46</v>
       </c>
       <c r="J135">
-        <v>3.4632</v>
+        <v>4.212</v>
       </c>
       <c r="K135">
-        <v>2.3428</v>
+        <v>2.7679</v>
       </c>
       <c r="L135" t="s">
         <v>15</v>
@@ -6396,10 +6399,10 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D136">
-        <v>1624</v>
+        <v>1610</v>
       </c>
       <c r="E136">
         <v>52</v>
@@ -6440,31 +6443,31 @@
         <v>136</v>
       </c>
       <c r="C137">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D137">
         <v>1624</v>
       </c>
       <c r="E137">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F137">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G137">
         <v>2</v>
       </c>
       <c r="H137">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I137">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J137">
-        <v>2.0881</v>
+        <v>2.3763</v>
       </c>
       <c r="K137">
-        <v>1.2732</v>
+        <v>1.4921</v>
       </c>
       <c r="L137" t="s">
         <v>15</v>
@@ -6572,16 +6575,16 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="D140">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="E140">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F140">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -6616,16 +6619,16 @@
         <v>140</v>
       </c>
       <c r="C141">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D141">
         <v>1624</v>
       </c>
       <c r="E141">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F141">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -6637,10 +6640,10 @@
         <v>21</v>
       </c>
       <c r="J141">
-        <v>1.1605</v>
+        <v>1.0695</v>
       </c>
       <c r="K141">
-        <v>1.1605</v>
+        <v>1.0695</v>
       </c>
       <c r="L141" t="s">
         <v>15</v>
@@ -6663,28 +6666,28 @@
         <v>1278</v>
       </c>
       <c r="D142">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="E142">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F142">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G142">
         <v>2</v>
       </c>
       <c r="H142">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="I142">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J142">
-        <v>2.1189</v>
+        <v>3.6473</v>
       </c>
       <c r="K142">
-        <v>1.2243</v>
+        <v>2.4315</v>
       </c>
       <c r="L142" t="s">
         <v>15</v>
@@ -6748,31 +6751,31 @@
         <v>143</v>
       </c>
       <c r="C144">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="D144">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="E144">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F144">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="I144">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J144">
-        <v>2.0718</v>
+        <v>1.1714</v>
       </c>
       <c r="K144">
-        <v>1.1301</v>
+        <v>1.1714</v>
       </c>
       <c r="L144" t="s">
         <v>15</v>
@@ -6792,31 +6795,31 @@
         <v>144</v>
       </c>
       <c r="C145">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D145">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="E145">
+        <v>50</v>
+      </c>
+      <c r="F145">
+        <v>1963.5</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="H145">
+        <v>68</v>
+      </c>
+      <c r="I145">
         <v>52</v>
       </c>
-      <c r="F145">
-        <v>2123.72</v>
-      </c>
-      <c r="G145">
-        <v>1</v>
-      </c>
-      <c r="H145">
-        <v>16</v>
-      </c>
-      <c r="I145">
-        <v>16</v>
-      </c>
       <c r="J145">
-        <v>0.7534</v>
+        <v>3.4632</v>
       </c>
       <c r="K145">
-        <v>0.7534</v>
+        <v>2.6483</v>
       </c>
       <c r="L145" t="s">
         <v>15</v>
@@ -6883,28 +6886,28 @@
         <v>1950</v>
       </c>
       <c r="D147">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="E147">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F147">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G147">
         <v>1</v>
       </c>
       <c r="H147">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I147">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J147">
-        <v>1.3816</v>
+        <v>1.1301</v>
       </c>
       <c r="K147">
-        <v>1.3816</v>
+        <v>1.1301</v>
       </c>
       <c r="L147" t="s">
         <v>15</v>
@@ -6924,31 +6927,31 @@
         <v>147</v>
       </c>
       <c r="C148">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D148">
         <v>1678</v>
       </c>
       <c r="E148">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F148">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G148">
         <v>1</v>
       </c>
       <c r="H148">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I148">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J148">
-        <v>3.2961</v>
+        <v>3.9789</v>
       </c>
       <c r="K148">
-        <v>3.2961</v>
+        <v>3.9789</v>
       </c>
       <c r="L148" t="s">
         <v>15</v>
@@ -6971,28 +6974,28 @@
         <v>859</v>
       </c>
       <c r="D149">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E149">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F149">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G149">
         <v>2</v>
       </c>
       <c r="H149">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I149">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J149">
-        <v>2.0718</v>
+        <v>3.1289</v>
       </c>
       <c r="K149">
-        <v>1.3184</v>
+        <v>2.1662</v>
       </c>
       <c r="L149" t="s">
         <v>15</v>
@@ -7015,13 +7018,13 @@
         <v>1111</v>
       </c>
       <c r="D150">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E150">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F150">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -7033,10 +7036,10 @@
         <v>16</v>
       </c>
       <c r="J150">
-        <v>0.8149</v>
+        <v>0.9628</v>
       </c>
       <c r="K150">
-        <v>0.8149</v>
+        <v>0.9628</v>
       </c>
       <c r="L150" t="s">
         <v>15</v>
@@ -7059,13 +7062,13 @@
         <v>1698</v>
       </c>
       <c r="D151">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E151">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F151">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -7077,10 +7080,10 @@
         <v>19</v>
       </c>
       <c r="J151">
-        <v>1.05</v>
+        <v>1.1433</v>
       </c>
       <c r="K151">
-        <v>1.05</v>
+        <v>1.1433</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -7144,16 +7147,16 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>1865</v>
+        <v>1853</v>
       </c>
       <c r="D153">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="E153">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F153">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -7276,16 +7279,16 @@
         <v>155</v>
       </c>
       <c r="C156">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="D156">
         <v>1679</v>
       </c>
       <c r="E156">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F156">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -7297,10 +7300,10 @@
         <v>38</v>
       </c>
       <c r="J156">
-        <v>1.9353</v>
+        <v>2.1</v>
       </c>
       <c r="K156">
-        <v>1.9353</v>
+        <v>2.1</v>
       </c>
       <c r="L156" t="s">
         <v>15</v>
@@ -7367,13 +7370,13 @@
         <v>1278</v>
       </c>
       <c r="D158">
-        <v>1680</v>
+        <v>1669</v>
       </c>
       <c r="E158">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F158">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -7408,10 +7411,10 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="D159">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="E159">
         <v>52</v>
@@ -7420,16 +7423,16 @@
         <v>2123.72</v>
       </c>
       <c r="G159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H159">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I159">
         <v>31</v>
       </c>
       <c r="J159">
-        <v>2.8252</v>
+        <v>1.4597</v>
       </c>
       <c r="K159">
         <v>1.4597</v>
@@ -7452,10 +7455,10 @@
         <v>159</v>
       </c>
       <c r="C160">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D160">
-        <v>1681</v>
+        <v>1670</v>
       </c>
       <c r="E160">
         <v>52</v>
@@ -7496,31 +7499,31 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D161">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="E161">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F161">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H161">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="I161">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J161">
-        <v>3.2605</v>
+        <v>3.7199</v>
       </c>
       <c r="K161">
-        <v>1.7131</v>
+        <v>1.4126</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -7543,7 +7546,7 @@
         <v>682</v>
       </c>
       <c r="D162">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="E162">
         <v>52</v>
@@ -7555,16 +7558,16 @@
         <v>1</v>
       </c>
       <c r="H162">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I162">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J162">
-        <v>3.6728</v>
+        <v>3.8612</v>
       </c>
       <c r="K162">
-        <v>3.6728</v>
+        <v>3.8612</v>
       </c>
       <c r="L162" t="s">
         <v>15</v>
@@ -7587,28 +7590,28 @@
         <v>1954</v>
       </c>
       <c r="D163">
-        <v>1733</v>
+        <v>1730</v>
       </c>
       <c r="E163">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F163">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G163">
         <v>2</v>
       </c>
       <c r="H163">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I163">
         <v>71</v>
       </c>
       <c r="J163">
-        <v>4.9183</v>
+        <v>4.1437</v>
       </c>
       <c r="K163">
-        <v>3.9236</v>
+        <v>3.3432</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7628,31 +7631,31 @@
         <v>163</v>
       </c>
       <c r="C164">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D164">
         <v>1734</v>
       </c>
       <c r="E164">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F164">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>0.9167</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>0.9167</v>
       </c>
       <c r="L164" t="s">
         <v>15</v>
@@ -7672,10 +7675,10 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="D165">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E165">
         <v>52</v>
@@ -7687,16 +7690,16 @@
         <v>1</v>
       </c>
       <c r="H165">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I165">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J165">
-        <v>1.3655</v>
+        <v>0.7534</v>
       </c>
       <c r="K165">
-        <v>1.3655</v>
+        <v>0.7534</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7719,28 +7722,28 @@
         <v>1111</v>
       </c>
       <c r="D166">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E166">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F166">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G166">
         <v>1</v>
       </c>
       <c r="H166">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I166">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J166">
-        <v>2.684</v>
+        <v>3.7908</v>
       </c>
       <c r="K166">
-        <v>2.684</v>
+        <v>3.7908</v>
       </c>
       <c r="L166" t="s">
         <v>15</v>
@@ -7760,10 +7763,10 @@
         <v>166</v>
       </c>
       <c r="C167">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="D167">
-        <v>1734</v>
+        <v>1741</v>
       </c>
       <c r="E167">
         <v>52</v>
@@ -7775,16 +7778,16 @@
         <v>3</v>
       </c>
       <c r="H167">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="I167">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J167">
-        <v>4.7087</v>
+        <v>3.4374</v>
       </c>
       <c r="K167">
-        <v>2.1189</v>
+        <v>1.8835</v>
       </c>
       <c r="L167" t="s">
         <v>15</v>
@@ -7848,16 +7851,16 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="D169">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="E169">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F169">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -7869,10 +7872,10 @@
         <v>82</v>
       </c>
       <c r="J169">
-        <v>4.5315</v>
+        <v>4.1762</v>
       </c>
       <c r="K169">
-        <v>4.5315</v>
+        <v>4.1762</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7892,10 +7895,10 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="D170">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="E170">
         <v>52</v>
@@ -7980,10 +7983,10 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D172">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E172">
         <v>52</v>
@@ -8068,10 +8071,10 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="D174">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="E174">
         <v>52</v>
@@ -8112,31 +8115,31 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="D175">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E175">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F175">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G175">
         <v>2</v>
       </c>
       <c r="H175">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I175">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J175">
-        <v>2.5465</v>
+        <v>3.2052</v>
       </c>
       <c r="K175">
-        <v>1.3751</v>
+        <v>1.7131</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8156,16 +8159,16 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D176">
-        <v>1735</v>
+        <v>1731</v>
       </c>
       <c r="E176">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F176">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -8177,10 +8180,10 @@
         <v>45</v>
       </c>
       <c r="J176">
-        <v>2.2918</v>
+        <v>2.1189</v>
       </c>
       <c r="K176">
-        <v>2.2918</v>
+        <v>2.1189</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8200,31 +8203,31 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>1699</v>
+        <v>1692</v>
       </c>
       <c r="D177">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="E177">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F177">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J177">
-        <v>2.0372</v>
+        <v>0</v>
       </c>
       <c r="K177">
-        <v>2.0372</v>
+        <v>0</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -8244,31 +8247,31 @@
         <v>177</v>
       </c>
       <c r="C178">
-        <v>1600</v>
+        <v>1621</v>
       </c>
       <c r="D178">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="E178">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F178">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I178">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>1.2158</v>
       </c>
       <c r="L178" t="s">
         <v>15</v>
@@ -8420,10 +8423,10 @@
         <v>181</v>
       </c>
       <c r="C182">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="D182">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E182">
         <v>52</v>
@@ -8435,16 +8438,16 @@
         <v>1</v>
       </c>
       <c r="H182">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I182">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J182">
-        <v>0.9417</v>
+        <v>1.9306</v>
       </c>
       <c r="K182">
-        <v>0.9417</v>
+        <v>1.9306</v>
       </c>
       <c r="L182" t="s">
         <v>15</v>
@@ -8464,31 +8467,31 @@
         <v>182</v>
       </c>
       <c r="C183">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="D183">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E183">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F183">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G183">
         <v>1</v>
       </c>
       <c r="H183">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I183">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J183">
-        <v>3.3903</v>
+        <v>3.7179</v>
       </c>
       <c r="K183">
-        <v>3.3903</v>
+        <v>3.7179</v>
       </c>
       <c r="L183" t="s">
         <v>15</v>
@@ -8511,28 +8514,28 @@
         <v>939</v>
       </c>
       <c r="D184">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E184">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F184">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G184">
         <v>1</v>
       </c>
       <c r="H184">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I184">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J184">
-        <v>1.4126</v>
+        <v>1.8789</v>
       </c>
       <c r="K184">
-        <v>1.4126</v>
+        <v>1.8789</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8596,10 +8599,10 @@
         <v>185</v>
       </c>
       <c r="C186">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D186">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="E186">
         <v>52</v>
@@ -8611,16 +8614,16 @@
         <v>2</v>
       </c>
       <c r="H186">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I186">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J186">
-        <v>3.767</v>
+        <v>4.0024</v>
       </c>
       <c r="K186">
-        <v>2.7311</v>
+        <v>2.9665</v>
       </c>
       <c r="L186" t="s">
         <v>15</v>
@@ -8684,10 +8687,10 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D188">
-        <v>1791</v>
+        <v>1802</v>
       </c>
       <c r="E188">
         <v>52</v>
@@ -8728,31 +8731,31 @@
         <v>188</v>
       </c>
       <c r="C189">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="D189">
         <v>1791</v>
       </c>
       <c r="E189">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F189">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G189">
         <v>1</v>
       </c>
       <c r="H189">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I189">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J189">
-        <v>0.8947000000000001</v>
+        <v>1.1714</v>
       </c>
       <c r="K189">
-        <v>0.8947000000000001</v>
+        <v>1.1714</v>
       </c>
       <c r="L189" t="s">
         <v>15</v>
@@ -8772,16 +8775,16 @@
         <v>189</v>
       </c>
       <c r="C190">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="D190">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E190">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F190">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -8793,10 +8796,10 @@
         <v>43</v>
       </c>
       <c r="J190">
-        <v>2.0248</v>
+        <v>2.19</v>
       </c>
       <c r="K190">
-        <v>2.0248</v>
+        <v>2.19</v>
       </c>
       <c r="L190" t="s">
         <v>15</v>
@@ -8907,28 +8910,28 @@
         <v>1449</v>
       </c>
       <c r="D193">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E193">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F193">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G193">
         <v>1</v>
       </c>
       <c r="H193">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I193">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J193">
-        <v>2.7781</v>
+        <v>3.371</v>
       </c>
       <c r="K193">
-        <v>2.7781</v>
+        <v>3.371</v>
       </c>
       <c r="L193" t="s">
         <v>15</v>
@@ -8992,16 +8995,16 @@
         <v>194</v>
       </c>
       <c r="C195">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D195">
         <v>1848</v>
       </c>
       <c r="E195">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F195">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -9036,10 +9039,10 @@
         <v>195</v>
       </c>
       <c r="C196">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D196">
-        <v>1848</v>
+        <v>1857</v>
       </c>
       <c r="E196">
         <v>52</v>
@@ -9124,16 +9127,16 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="D198">
         <v>1848</v>
       </c>
       <c r="E198">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F198">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -9145,10 +9148,10 @@
         <v>24</v>
       </c>
       <c r="J198">
-        <v>1.2223</v>
+        <v>1.3263</v>
       </c>
       <c r="K198">
-        <v>1.2223</v>
+        <v>1.3263</v>
       </c>
       <c r="L198" t="s">
         <v>15</v>
@@ -9212,31 +9215,31 @@
         <v>199</v>
       </c>
       <c r="C200">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D200">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="E200">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F200">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G200">
         <v>2</v>
       </c>
       <c r="H200">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I200">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J200">
-        <v>3.8141</v>
+        <v>3.5141</v>
       </c>
       <c r="K200">
-        <v>1.9306</v>
+        <v>2.2409</v>
       </c>
       <c r="L200" t="s">
         <v>15</v>
@@ -9300,7 +9303,7 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="D202">
         <v>1849</v>
@@ -9388,31 +9391,31 @@
         <v>203</v>
       </c>
       <c r="C204">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D204">
         <v>1849</v>
       </c>
       <c r="E204">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F204">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G204">
         <v>2</v>
       </c>
       <c r="H204">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I204">
         <v>38</v>
       </c>
       <c r="J204">
-        <v>3.249</v>
+        <v>3.4263</v>
       </c>
       <c r="K204">
-        <v>1.7893</v>
+        <v>2.1</v>
       </c>
       <c r="L204" t="s">
         <v>15</v>
@@ -9432,10 +9435,10 @@
         <v>204</v>
       </c>
       <c r="C205">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D205">
-        <v>1849</v>
+        <v>1839</v>
       </c>
       <c r="E205">
         <v>52</v>
@@ -9520,16 +9523,16 @@
         <v>206</v>
       </c>
       <c r="C207">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D207">
         <v>1849</v>
       </c>
       <c r="E207">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F207">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -9541,10 +9544,10 @@
         <v>42</v>
       </c>
       <c r="J207">
-        <v>1.9777</v>
+        <v>2.321</v>
       </c>
       <c r="K207">
-        <v>1.9777</v>
+        <v>2.321</v>
       </c>
       <c r="L207" t="s">
         <v>15</v>
@@ -9564,31 +9567,31 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="D208">
         <v>1849</v>
       </c>
       <c r="E208">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F208">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G208">
         <v>1</v>
       </c>
       <c r="H208">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I208">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J208">
-        <v>2.5898</v>
+        <v>3.0558</v>
       </c>
       <c r="K208">
-        <v>2.5898</v>
+        <v>3.0558</v>
       </c>
       <c r="L208" t="s">
         <v>15</v>
@@ -9608,10 +9611,10 @@
         <v>208</v>
       </c>
       <c r="C209">
-        <v>1621</v>
+        <v>1617</v>
       </c>
       <c r="D209">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="E209">
         <v>52</v>
@@ -9652,10 +9655,10 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="D210">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="E210">
         <v>52</v>
@@ -9696,31 +9699,31 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D211">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="E211">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F211">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G211">
         <v>2</v>
       </c>
       <c r="H211">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I211">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J211">
-        <v>3.249</v>
+        <v>3.5651</v>
       </c>
       <c r="K211">
-        <v>2.3544</v>
+        <v>2.7502</v>
       </c>
       <c r="L211" t="s">
         <v>15</v>
@@ -9740,10 +9743,10 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D212">
-        <v>1906</v>
+        <v>1915</v>
       </c>
       <c r="E212">
         <v>52</v>
@@ -9755,16 +9758,16 @@
         <v>1</v>
       </c>
       <c r="H212">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="I212">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="J212">
-        <v>3.0607</v>
+        <v>1.3655</v>
       </c>
       <c r="K212">
-        <v>3.0607</v>
+        <v>1.3655</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9784,10 +9787,10 @@
         <v>212</v>
       </c>
       <c r="C213">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D213">
-        <v>1906</v>
+        <v>1918</v>
       </c>
       <c r="E213">
         <v>52</v>
@@ -9796,19 +9799,19 @@
         <v>2123.72</v>
       </c>
       <c r="G213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="I213">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="J213">
-        <v>5.3679</v>
+        <v>0</v>
       </c>
       <c r="K213">
-        <v>5.3679</v>
+        <v>0</v>
       </c>
       <c r="L213" t="s">
         <v>15</v>
@@ -9828,10 +9831,10 @@
         <v>213</v>
       </c>
       <c r="C214">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="D214">
-        <v>1906</v>
+        <v>1913</v>
       </c>
       <c r="E214">
         <v>52</v>
@@ -9875,7 +9878,7 @@
         <v>1281</v>
       </c>
       <c r="D215">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="E215">
         <v>52</v>
@@ -9916,10 +9919,10 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="D216">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="E216">
         <v>52</v>
@@ -10048,16 +10051,16 @@
         <v>218</v>
       </c>
       <c r="C219">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D219">
         <v>1907</v>
       </c>
       <c r="E219">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F219">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G219">
         <v>1</v>
@@ -10069,10 +10072,10 @@
         <v>19</v>
       </c>
       <c r="J219">
-        <v>0.8947000000000001</v>
+        <v>0.9677</v>
       </c>
       <c r="K219">
-        <v>0.8947000000000001</v>
+        <v>0.9677</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -10092,10 +10095,10 @@
         <v>219</v>
       </c>
       <c r="C220">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D220">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="E220">
         <v>52</v>
@@ -10139,7 +10142,7 @@
         <v>1453</v>
       </c>
       <c r="D221">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="E221">
         <v>52</v>
@@ -10151,16 +10154,16 @@
         <v>2</v>
       </c>
       <c r="H221">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I221">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J221">
-        <v>5.8388</v>
+        <v>6.2626</v>
       </c>
       <c r="K221">
-        <v>5.0854</v>
+        <v>5.5092</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -10224,31 +10227,31 @@
         <v>222</v>
       </c>
       <c r="C223">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="D223">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="E223">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F223">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G223">
         <v>1</v>
       </c>
       <c r="H223">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I223">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J223">
-        <v>2.4015</v>
+        <v>2.6993</v>
       </c>
       <c r="K223">
-        <v>2.4015</v>
+        <v>2.6993</v>
       </c>
       <c r="L223" t="s">
         <v>15</v>
@@ -10268,16 +10271,16 @@
         <v>223</v>
       </c>
       <c r="C224">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="D224">
         <v>1907</v>
       </c>
       <c r="E224">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F224">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G224">
         <v>1</v>
@@ -10289,10 +10292,10 @@
         <v>90</v>
       </c>
       <c r="J224">
-        <v>4.5837</v>
+        <v>4.9736</v>
       </c>
       <c r="K224">
-        <v>4.5837</v>
+        <v>4.9736</v>
       </c>
       <c r="L224" t="s">
         <v>15</v>
@@ -10356,16 +10359,16 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D226">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="E226">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F226">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -10403,7 +10406,7 @@
         <v>758</v>
       </c>
       <c r="D227">
-        <v>1965</v>
+        <v>1953</v>
       </c>
       <c r="E227">
         <v>52</v>
@@ -10488,10 +10491,10 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="D229">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="E229">
         <v>50</v>
@@ -10532,10 +10535,10 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D230">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="E230">
         <v>52</v>
@@ -10547,16 +10550,16 @@
         <v>2</v>
       </c>
       <c r="H230">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I230">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J230">
-        <v>3.2019</v>
+        <v>3.1548</v>
       </c>
       <c r="K230">
-        <v>2.2131</v>
+        <v>2.166</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10708,31 +10711,31 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="D234">
         <v>1966</v>
       </c>
       <c r="E234">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F234">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H234">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I234">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J234">
-        <v>6.7806</v>
+        <v>6.4681</v>
       </c>
       <c r="K234">
-        <v>5.7446</v>
+        <v>6.4681</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10840,16 +10843,16 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D237">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E237">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F237">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G237">
         <v>1</v>
@@ -10861,10 +10864,10 @@
         <v>78</v>
       </c>
       <c r="J237">
-        <v>3.6728</v>
+        <v>4.3104</v>
       </c>
       <c r="K237">
-        <v>3.6728</v>
+        <v>4.3104</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10928,10 +10931,10 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="D239">
-        <v>1968</v>
+        <v>1957</v>
       </c>
       <c r="E239">
         <v>52</v>
@@ -10940,19 +10943,19 @@
         <v>2123.72</v>
       </c>
       <c r="G239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H239">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="I239">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J239">
-        <v>2.0248</v>
+        <v>3.8612</v>
       </c>
       <c r="K239">
-        <v>2.0248</v>
+        <v>2.0718</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -11063,7 +11066,7 @@
         <v>1984</v>
       </c>
       <c r="D242">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E242">
         <v>52</v>
@@ -11192,10 +11195,10 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="D245">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E245">
         <v>52</v>
@@ -11239,13 +11242,13 @@
         <v>667</v>
       </c>
       <c r="D246">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E246">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F246">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -11324,7 +11327,7 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="D248">
         <v>2027</v>
@@ -11368,7 +11371,7 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>1440</v>
+        <v>1454</v>
       </c>
       <c r="D249">
         <v>2027</v>
@@ -11380,19 +11383,19 @@
         <v>2123.72</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I249">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1.1301</v>
       </c>
       <c r="K249">
-        <v>0</v>
+        <v>1.1301</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11412,31 +11415,31 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>1712</v>
+        <v>1723</v>
       </c>
       <c r="D250">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="E250">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F250">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H250">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="I250">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="J250">
-        <v>1.5645</v>
+        <v>3.5315</v>
       </c>
       <c r="K250">
-        <v>1.5645</v>
+        <v>2.3073</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11456,16 +11459,16 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>1798</v>
+        <v>1811</v>
       </c>
       <c r="D251">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E251">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F251">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G251">
         <v>0</v>
@@ -11544,10 +11547,10 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="D253">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="E253">
         <v>52</v>
@@ -11632,7 +11635,7 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D255">
         <v>2036</v>
@@ -11720,37 +11723,37 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D257">
-        <v>1966</v>
+        <v>1992</v>
       </c>
       <c r="E257">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F257">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="I257">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="J257">
-        <v>0</v>
+        <v>7.6281</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>7.6281</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
       </c>
       <c r="M257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N257">
         <v>0.2</v>
@@ -11785,40 +11788,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -11829,10 +11832,10 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>1.6331</v>
+        <v>1.7786</v>
       </c>
       <c r="D2">
-        <v>10.5884</v>
+        <v>13.5479</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11841,7 +11844,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -11850,16 +11853,16 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Images_BGA/Results/Reports/PCBA2_06_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_06_inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
   <si>
     <t>image_name</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>PASS</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>total_balls</t>
@@ -503,16 +500,16 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1574</v>
+        <v>1685</v>
       </c>
       <c r="D2">
-        <v>1187</v>
+        <v>1167</v>
       </c>
       <c r="E2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F2">
-        <v>2123.72</v>
+        <v>1385.44</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -547,10 +544,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1962</v>
+        <v>1626</v>
       </c>
       <c r="D3">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -591,31 +588,31 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1835</v>
+        <v>1951</v>
       </c>
       <c r="D4">
-        <v>1205</v>
+        <v>1190</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F4">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>6.7736</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>3.7179</v>
+        <v>0</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -635,10 +632,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>941</v>
+        <v>768</v>
       </c>
       <c r="D5">
-        <v>1206</v>
+        <v>1192</v>
       </c>
       <c r="E5">
         <v>52</v>
@@ -647,19 +644,19 @@
         <v>2123.72</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>4.8971</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>4.8971</v>
+        <v>0</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -679,31 +676,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1117</v>
+        <v>1820</v>
       </c>
       <c r="D6">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F6">
-        <v>1963.5</v>
+        <v>1256.64</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>6.0479</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>6.0479</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -723,16 +720,16 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>1195</v>
+        <v>945</v>
       </c>
       <c r="D7">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>1661.9</v>
+        <v>1385.44</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -767,31 +764,31 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1274</v>
+        <v>1898</v>
       </c>
       <c r="D8">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>1661.9</v>
+        <v>1385.44</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>6.4239</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>6.4239</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -811,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1353</v>
+        <v>1117</v>
       </c>
       <c r="D9">
-        <v>1210</v>
+        <v>1202</v>
       </c>
       <c r="E9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.9628</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.9628</v>
+        <v>0</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -855,31 +852,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1431</v>
+        <v>1195</v>
       </c>
       <c r="D10">
         <v>1210</v>
       </c>
       <c r="E10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10">
-        <v>1520.53</v>
+        <v>1661.9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>2.6307</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>1.5784</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -899,16 +896,16 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1511</v>
+        <v>1274</v>
       </c>
       <c r="D11">
         <v>1210</v>
       </c>
       <c r="E11">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -943,16 +940,16 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>1667</v>
+        <v>1353</v>
       </c>
       <c r="D12">
         <v>1210</v>
       </c>
       <c r="E12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -964,10 +961,10 @@
         <v>16</v>
       </c>
       <c r="J12">
-        <v>0.8842</v>
+        <v>0.9628</v>
       </c>
       <c r="K12">
-        <v>0.8842</v>
+        <v>0.9628</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -987,31 +984,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1748</v>
+        <v>1431</v>
       </c>
       <c r="D13">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="E13">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F13">
-        <v>2123.72</v>
+        <v>1520.53</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J13">
-        <v>1.4126</v>
+        <v>2.6307</v>
       </c>
       <c r="K13">
-        <v>1.4126</v>
+        <v>1.5784</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1031,16 +1028,16 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>880</v>
+        <v>1511</v>
       </c>
       <c r="D14">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1075,7 +1072,7 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>1038</v>
+        <v>880</v>
       </c>
       <c r="D15">
         <v>1211</v>
@@ -1087,19 +1084,19 @@
         <v>1661.9</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>1.3238</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>1.3238</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1119,31 +1116,31 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>717</v>
+        <v>1038</v>
       </c>
       <c r="D16">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I16">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J16">
-        <v>3.0394</v>
+        <v>1.3238</v>
       </c>
       <c r="K16">
-        <v>2.1552</v>
+        <v>1.3238</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1163,31 +1160,31 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>775</v>
+        <v>719</v>
       </c>
       <c r="D17">
         <v>1212</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F17">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4.3926</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2.4671</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -1207,31 +1204,31 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>787</v>
+        <v>719</v>
       </c>
       <c r="D18">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E18">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F18">
-        <v>1661.9</v>
+        <v>1385.44</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3.9699</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>3.9699</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -1251,31 +1248,31 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>1945</v>
+        <v>790</v>
       </c>
       <c r="D19">
-        <v>1257</v>
+        <v>1243</v>
       </c>
       <c r="E19">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F19">
-        <v>1134.11</v>
+        <v>2123.72</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>9.5228</v>
+        <v>0</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1383,31 +1380,31 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="D22">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="E22">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F22">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2.2264</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1.2034</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1427,31 +1424,31 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>716</v>
+        <v>1926</v>
       </c>
       <c r="D23">
         <v>1258</v>
       </c>
       <c r="E23">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F23">
-        <v>1520.53</v>
+        <v>1809.56</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>3.6172</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>3.6172</v>
+        <v>0</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1471,31 +1468,31 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="D24">
-        <v>1295</v>
+        <v>1260</v>
       </c>
       <c r="E24">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F24">
-        <v>1134.11</v>
+        <v>1661.9</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1.6848</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1.6848</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1603,16 +1600,16 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="D27">
         <v>1260</v>
       </c>
       <c r="E27">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F27">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1779,31 +1776,31 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1754</v>
+        <v>1761</v>
       </c>
       <c r="D31">
-        <v>1297</v>
+        <v>1260</v>
       </c>
       <c r="E31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F31">
-        <v>1134.11</v>
+        <v>1385.44</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1.6601</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1.6601</v>
       </c>
       <c r="L31" t="s">
         <v>15</v>
@@ -1911,16 +1908,16 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>1754</v>
+        <v>1930</v>
       </c>
       <c r="D34">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E34">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>1520.53</v>
+        <v>1809.56</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1955,10 +1952,10 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>1433</v>
+        <v>1754</v>
       </c>
       <c r="D35">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E35">
         <v>44</v>
@@ -1999,31 +1996,31 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>1515</v>
+        <v>1433</v>
       </c>
       <c r="D36">
         <v>1309</v>
       </c>
       <c r="E36">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F36">
-        <v>1809.56</v>
+        <v>1520.53</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>3.1499</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>1.6026</v>
+        <v>0</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2043,31 +2040,31 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>1594</v>
+        <v>1515</v>
       </c>
       <c r="D37">
         <v>1309</v>
       </c>
       <c r="E37">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F37">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>3.1499</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1.6026</v>
       </c>
       <c r="L37" t="s">
         <v>15</v>
@@ -2087,7 +2084,7 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>1674</v>
+        <v>1594</v>
       </c>
       <c r="D38">
         <v>1309</v>
@@ -2099,19 +2096,19 @@
         <v>1661.9</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>1.4441</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>1.4441</v>
+        <v>0</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2131,31 +2128,31 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1827</v>
+        <v>1674</v>
       </c>
       <c r="D39">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E39">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F39">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1.4441</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1.4441</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2175,10 +2172,10 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>708</v>
+        <v>1827</v>
       </c>
       <c r="D40">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="E40">
         <v>52</v>
@@ -2187,19 +2184,19 @@
         <v>2123.72</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>1.3184</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>1.3184</v>
+        <v>0</v>
       </c>
       <c r="L40" t="s">
         <v>15</v>
@@ -2219,7 +2216,7 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>786</v>
+        <v>708</v>
       </c>
       <c r="D41">
         <v>1308</v>
@@ -2231,19 +2228,19 @@
         <v>2123.72</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1.3184</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1.3184</v>
       </c>
       <c r="L41" t="s">
         <v>15</v>
@@ -2263,31 +2260,31 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>872</v>
+        <v>786</v>
       </c>
       <c r="D42">
         <v>1308</v>
       </c>
       <c r="E42">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F42">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>1.745</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>1.745</v>
+        <v>0</v>
       </c>
       <c r="L42" t="s">
         <v>15</v>
@@ -2307,31 +2304,31 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>948</v>
+        <v>872</v>
       </c>
       <c r="D43">
-        <v>1345</v>
+        <v>1308</v>
       </c>
       <c r="E43">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F43">
-        <v>1134.11</v>
+        <v>1661.9</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I43">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J43">
-        <v>3.2625</v>
+        <v>1.745</v>
       </c>
       <c r="K43">
-        <v>1.8517</v>
+        <v>1.745</v>
       </c>
       <c r="L43" t="s">
         <v>15</v>
@@ -2351,16 +2348,16 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>1028</v>
+        <v>956</v>
       </c>
       <c r="D44">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F44">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2395,16 +2392,16 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>1116</v>
+        <v>1028</v>
       </c>
       <c r="D45">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="E45">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F45">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2439,16 +2436,16 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>1195</v>
+        <v>1116</v>
       </c>
       <c r="D46">
-        <v>1347</v>
+        <v>1310</v>
       </c>
       <c r="E46">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F46">
-        <v>1134.11</v>
+        <v>1661.9</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2483,7 +2480,7 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>1274</v>
+        <v>1195</v>
       </c>
       <c r="D47">
         <v>1310</v>
@@ -2527,7 +2524,7 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>1355</v>
+        <v>1274</v>
       </c>
       <c r="D48">
         <v>1310</v>
@@ -2571,34 +2568,34 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>1938</v>
+        <v>1355</v>
       </c>
       <c r="D49">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E49">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F49">
-        <v>1520.53</v>
+        <v>1661.9</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>13.5479</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>13.5479</v>
+        <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -2615,7 +2612,7 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D50">
         <v>1358</v>
@@ -3187,10 +3184,10 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>1843</v>
+        <v>1595</v>
       </c>
       <c r="D63">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E63">
         <v>48</v>
@@ -3199,19 +3196,19 @@
         <v>1809.56</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="I63">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J63">
-        <v>1.8789</v>
+        <v>3.8683</v>
       </c>
       <c r="K63">
-        <v>1.8789</v>
+        <v>2.2657</v>
       </c>
       <c r="L63" t="s">
         <v>15</v>
@@ -3231,10 +3228,10 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>1434</v>
+        <v>1843</v>
       </c>
       <c r="D64">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E64">
         <v>48</v>
@@ -3243,19 +3240,19 @@
         <v>1809.56</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>1.8789</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>1.8789</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3275,10 +3272,10 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>1594</v>
+        <v>1434</v>
       </c>
       <c r="D65">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E65">
         <v>48</v>
@@ -3287,19 +3284,19 @@
         <v>1809.56</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>3.8683</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>2.2657</v>
+        <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3319,31 +3316,31 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>1943</v>
+        <v>1761</v>
       </c>
       <c r="D66">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="E66">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F66">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>5.0383</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>3.6257</v>
+        <v>0</v>
       </c>
       <c r="L66" t="s">
         <v>15</v>
@@ -3363,31 +3360,31 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>1761</v>
+        <v>701</v>
       </c>
       <c r="D67">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="E67">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F67">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>1.7422</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>1.7422</v>
       </c>
       <c r="L67" t="s">
         <v>15</v>
@@ -3407,31 +3404,31 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>701</v>
+        <v>875</v>
       </c>
       <c r="D68">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="E68">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F68">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I68">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>1.7422</v>
+        <v>0</v>
       </c>
       <c r="K68">
-        <v>1.7422</v>
+        <v>0</v>
       </c>
       <c r="L68" t="s">
         <v>15</v>
@@ -3451,31 +3448,31 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>875</v>
+        <v>953</v>
       </c>
       <c r="D69">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E69">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F69">
-        <v>1809.56</v>
+        <v>1520.53</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>3.5514</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>2.3676</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -3495,31 +3492,31 @@
         <v>69</v>
       </c>
       <c r="C70">
-        <v>953</v>
+        <v>1196</v>
       </c>
       <c r="D70">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="E70">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F70">
-        <v>1520.53</v>
+        <v>1809.56</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>3.5514</v>
+        <v>0</v>
       </c>
       <c r="K70">
-        <v>2.3676</v>
+        <v>0</v>
       </c>
       <c r="L70" t="s">
         <v>15</v>
@@ -3539,31 +3536,31 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>1026</v>
+        <v>1276</v>
       </c>
       <c r="D71">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="E71">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F71">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>1.4921</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>1.4921</v>
       </c>
       <c r="L71" t="s">
         <v>15</v>
@@ -3583,31 +3580,31 @@
         <v>71</v>
       </c>
       <c r="C72">
-        <v>1109</v>
+        <v>1443</v>
       </c>
       <c r="D72">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E72">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F72">
-        <v>1134.11</v>
+        <v>1963.5</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>2.2044</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>2.2044</v>
+        <v>0</v>
       </c>
       <c r="L72" t="s">
         <v>15</v>
@@ -3627,10 +3624,10 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>1196</v>
+        <v>1599</v>
       </c>
       <c r="D73">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E73">
         <v>48</v>
@@ -3639,19 +3636,19 @@
         <v>1809.56</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>0.8842</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>0.8842</v>
       </c>
       <c r="L73" t="s">
         <v>15</v>
@@ -3671,31 +3668,31 @@
         <v>73</v>
       </c>
       <c r="C74">
-        <v>1276</v>
+        <v>1679</v>
       </c>
       <c r="D74">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="E74">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F74">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I74">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J74">
-        <v>1.4921</v>
+        <v>0.7534</v>
       </c>
       <c r="K74">
-        <v>1.4921</v>
+        <v>0.7534</v>
       </c>
       <c r="L74" t="s">
         <v>15</v>
@@ -3715,31 +3712,31 @@
         <v>74</v>
       </c>
       <c r="C75">
-        <v>1599</v>
+        <v>1850</v>
       </c>
       <c r="D75">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="E75">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F75">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="I75">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J75">
-        <v>0.8842</v>
+        <v>3.1067</v>
       </c>
       <c r="K75">
-        <v>0.8842</v>
+        <v>2.139</v>
       </c>
       <c r="L75" t="s">
         <v>15</v>
@@ -3759,31 +3756,31 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>1679</v>
+        <v>787</v>
       </c>
       <c r="D76">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="E76">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F76">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="I76">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="J76">
-        <v>0.7534</v>
+        <v>3.0394</v>
       </c>
       <c r="K76">
-        <v>0.7534</v>
+        <v>3.0394</v>
       </c>
       <c r="L76" t="s">
         <v>15</v>
@@ -3803,31 +3800,31 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1850</v>
+        <v>1024</v>
       </c>
       <c r="D77">
         <v>1415</v>
       </c>
       <c r="E77">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F77">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J77">
-        <v>3.1067</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>2.139</v>
+        <v>0</v>
       </c>
       <c r="L77" t="s">
         <v>15</v>
@@ -3847,7 +3844,7 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>787</v>
+        <v>1116</v>
       </c>
       <c r="D78">
         <v>1413</v>
@@ -3862,16 +3859,16 @@
         <v>1</v>
       </c>
       <c r="H78">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I78">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J78">
-        <v>3.0394</v>
+        <v>1.3263</v>
       </c>
       <c r="K78">
-        <v>3.0394</v>
+        <v>1.3263</v>
       </c>
       <c r="L78" t="s">
         <v>15</v>
@@ -3935,10 +3932,10 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>1443</v>
+        <v>1521</v>
       </c>
       <c r="D80">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="E80">
         <v>50</v>
@@ -3979,31 +3976,31 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>1520</v>
+        <v>1940</v>
       </c>
       <c r="D81">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E81">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F81">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>5.0383</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>3.6257</v>
       </c>
       <c r="L81" t="s">
         <v>15</v>
@@ -4111,16 +4108,16 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>1121</v>
+        <v>1602</v>
       </c>
       <c r="D84">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="E84">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F84">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -4155,16 +4152,16 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>1602</v>
+        <v>1684</v>
       </c>
       <c r="D85">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E85">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F85">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -4199,7 +4196,7 @@
         <v>85</v>
       </c>
       <c r="C86">
-        <v>1684</v>
+        <v>1764</v>
       </c>
       <c r="D86">
         <v>1463</v>
@@ -4243,16 +4240,16 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>1764</v>
+        <v>1849</v>
       </c>
       <c r="D87">
         <v>1463</v>
       </c>
       <c r="E87">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F87">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -4287,10 +4284,10 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>1849</v>
+        <v>787</v>
       </c>
       <c r="D88">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E88">
         <v>50</v>
@@ -4299,19 +4296,19 @@
         <v>1963.5</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>3.5141</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>3.5141</v>
       </c>
       <c r="L88" t="s">
         <v>15</v>
@@ -4331,31 +4328,31 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>787</v>
+        <v>873</v>
       </c>
       <c r="D89">
         <v>1464</v>
       </c>
       <c r="E89">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F89">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="I89">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="J89">
-        <v>3.5141</v>
+        <v>2.3467</v>
       </c>
       <c r="K89">
-        <v>3.5141</v>
+        <v>2.3467</v>
       </c>
       <c r="L89" t="s">
         <v>15</v>
@@ -4375,31 +4372,31 @@
         <v>89</v>
       </c>
       <c r="C90">
-        <v>873</v>
+        <v>1037</v>
       </c>
       <c r="D90">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E90">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F90">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G90">
         <v>1</v>
       </c>
       <c r="H90">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I90">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J90">
-        <v>2.3467</v>
+        <v>1.3263</v>
       </c>
       <c r="K90">
-        <v>2.3467</v>
+        <v>1.3263</v>
       </c>
       <c r="L90" t="s">
         <v>15</v>
@@ -4419,31 +4416,31 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>1037</v>
+        <v>1118</v>
       </c>
       <c r="D91">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E91">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F91">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I91">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J91">
-        <v>1.3263</v>
+        <v>0</v>
       </c>
       <c r="K91">
-        <v>1.3263</v>
+        <v>0</v>
       </c>
       <c r="L91" t="s">
         <v>15</v>
@@ -4727,31 +4724,31 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>1951</v>
+        <v>695</v>
       </c>
       <c r="D98">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="E98">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F98">
-        <v>1520.53</v>
+        <v>1963.5</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I98">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J98">
-        <v>1.0523</v>
+        <v>0</v>
       </c>
       <c r="K98">
-        <v>1.0523</v>
+        <v>0</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4771,31 +4768,31 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>695</v>
+        <v>1685</v>
       </c>
       <c r="D99">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F99">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>1.8237</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>1.8237</v>
       </c>
       <c r="L99" t="s">
         <v>15</v>
@@ -4815,31 +4812,31 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>1685</v>
+        <v>1943</v>
       </c>
       <c r="D100">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="E100">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F100">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G100">
         <v>1</v>
       </c>
       <c r="H100">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I100">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J100">
-        <v>1.8237</v>
+        <v>0.7534</v>
       </c>
       <c r="K100">
-        <v>1.8237</v>
+        <v>0.7534</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -6091,7 +6088,7 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="D129">
         <v>1573</v>
@@ -6179,31 +6176,31 @@
         <v>130</v>
       </c>
       <c r="C131">
-        <v>1107</v>
+        <v>1694</v>
       </c>
       <c r="D131">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="E131">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F131">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G131">
         <v>1</v>
       </c>
       <c r="H131">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I131">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J131">
-        <v>0.8149</v>
+        <v>2.106</v>
       </c>
       <c r="K131">
-        <v>0.8149</v>
+        <v>2.106</v>
       </c>
       <c r="L131" t="s">
         <v>15</v>
@@ -6223,31 +6220,31 @@
         <v>131</v>
       </c>
       <c r="C132">
-        <v>1694</v>
+        <v>1776</v>
       </c>
       <c r="D132">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="E132">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F132">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G132">
         <v>1</v>
       </c>
       <c r="H132">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I132">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J132">
-        <v>2.106</v>
+        <v>0.8842</v>
       </c>
       <c r="K132">
-        <v>2.106</v>
+        <v>0.8842</v>
       </c>
       <c r="L132" t="s">
         <v>15</v>
@@ -6267,7 +6264,7 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>1776</v>
+        <v>1861</v>
       </c>
       <c r="D133">
         <v>1623</v>
@@ -6282,16 +6279,16 @@
         <v>1</v>
       </c>
       <c r="H133">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I133">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J133">
-        <v>0.8842</v>
+        <v>1.5473</v>
       </c>
       <c r="K133">
-        <v>0.8842</v>
+        <v>1.5473</v>
       </c>
       <c r="L133" t="s">
         <v>15</v>
@@ -6311,31 +6308,31 @@
         <v>133</v>
       </c>
       <c r="C134">
-        <v>1861</v>
+        <v>1944</v>
       </c>
       <c r="D134">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="E134">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F134">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="I134">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J134">
-        <v>1.5473</v>
+        <v>4.212</v>
       </c>
       <c r="K134">
-        <v>1.5473</v>
+        <v>2.7679</v>
       </c>
       <c r="L134" t="s">
         <v>15</v>
@@ -6355,31 +6352,31 @@
         <v>134</v>
       </c>
       <c r="C135">
-        <v>1944</v>
+        <v>778</v>
       </c>
       <c r="D135">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="E135">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F135">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G135">
         <v>2</v>
       </c>
       <c r="H135">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I135">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J135">
-        <v>4.212</v>
+        <v>4.5204</v>
       </c>
       <c r="K135">
-        <v>2.7679</v>
+        <v>2.4015</v>
       </c>
       <c r="L135" t="s">
         <v>15</v>
@@ -6399,31 +6396,31 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>776</v>
+        <v>865</v>
       </c>
       <c r="D136">
-        <v>1610</v>
+        <v>1624</v>
       </c>
       <c r="E136">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F136">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G136">
         <v>2</v>
       </c>
       <c r="H136">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="I136">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="J136">
-        <v>4.5204</v>
+        <v>2.3763</v>
       </c>
       <c r="K136">
-        <v>2.4015</v>
+        <v>1.4921</v>
       </c>
       <c r="L136" t="s">
         <v>15</v>
@@ -6443,31 +6440,31 @@
         <v>136</v>
       </c>
       <c r="C137">
-        <v>865</v>
+        <v>945</v>
       </c>
       <c r="D137">
         <v>1624</v>
       </c>
       <c r="E137">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F137">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="I137">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="J137">
-        <v>2.3763</v>
+        <v>3.2019</v>
       </c>
       <c r="K137">
-        <v>1.4921</v>
+        <v>3.2019</v>
       </c>
       <c r="L137" t="s">
         <v>15</v>
@@ -6487,7 +6484,7 @@
         <v>137</v>
       </c>
       <c r="C138">
-        <v>945</v>
+        <v>1029</v>
       </c>
       <c r="D138">
         <v>1624</v>
@@ -6502,16 +6499,16 @@
         <v>1</v>
       </c>
       <c r="H138">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="I138">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="J138">
-        <v>3.2019</v>
+        <v>3.8612</v>
       </c>
       <c r="K138">
-        <v>3.2019</v>
+        <v>3.8612</v>
       </c>
       <c r="L138" t="s">
         <v>15</v>
@@ -6531,31 +6528,31 @@
         <v>138</v>
       </c>
       <c r="C139">
-        <v>1029</v>
+        <v>1525</v>
       </c>
       <c r="D139">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="E139">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F139">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="I139">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="J139">
-        <v>3.8612</v>
+        <v>0</v>
       </c>
       <c r="K139">
-        <v>3.8612</v>
+        <v>0</v>
       </c>
       <c r="L139" t="s">
         <v>15</v>
@@ -6575,10 +6572,10 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>1525</v>
+        <v>1611</v>
       </c>
       <c r="D140">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="E140">
         <v>50</v>
@@ -6587,19 +6584,19 @@
         <v>1963.5</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>1.0695</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1.0695</v>
       </c>
       <c r="L140" t="s">
         <v>15</v>
@@ -6619,31 +6616,31 @@
         <v>140</v>
       </c>
       <c r="C141">
-        <v>1611</v>
+        <v>1278</v>
       </c>
       <c r="D141">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="E141">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F141">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I141">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J141">
-        <v>1.0695</v>
+        <v>3.6473</v>
       </c>
       <c r="K141">
-        <v>1.0695</v>
+        <v>2.4315</v>
       </c>
       <c r="L141" t="s">
         <v>15</v>
@@ -6663,31 +6660,31 @@
         <v>141</v>
       </c>
       <c r="C142">
-        <v>1278</v>
+        <v>1361</v>
       </c>
       <c r="D142">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="E142">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F142">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="I142">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="J142">
-        <v>3.6473</v>
+        <v>1.1772</v>
       </c>
       <c r="K142">
-        <v>2.4315</v>
+        <v>1.1772</v>
       </c>
       <c r="L142" t="s">
         <v>15</v>
@@ -6707,31 +6704,31 @@
         <v>142</v>
       </c>
       <c r="C143">
-        <v>1361</v>
+        <v>1197</v>
       </c>
       <c r="D143">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="E143">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F143">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G143">
         <v>1</v>
       </c>
       <c r="H143">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I143">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J143">
-        <v>1.1772</v>
+        <v>1.1714</v>
       </c>
       <c r="K143">
-        <v>1.1772</v>
+        <v>1.1714</v>
       </c>
       <c r="L143" t="s">
         <v>15</v>
@@ -6751,10 +6748,10 @@
         <v>143</v>
       </c>
       <c r="C144">
-        <v>1197</v>
+        <v>1108</v>
       </c>
       <c r="D144">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E144">
         <v>50</v>
@@ -6766,16 +6763,16 @@
         <v>1</v>
       </c>
       <c r="H144">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I144">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J144">
-        <v>1.1714</v>
+        <v>0.8149</v>
       </c>
       <c r="K144">
-        <v>1.1714</v>
+        <v>0.8149</v>
       </c>
       <c r="L144" t="s">
         <v>15</v>
@@ -7411,10 +7408,10 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1445</v>
+        <v>1362</v>
       </c>
       <c r="D159">
-        <v>1683</v>
+        <v>1670</v>
       </c>
       <c r="E159">
         <v>52</v>
@@ -7426,16 +7423,16 @@
         <v>1</v>
       </c>
       <c r="H159">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I159">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J159">
-        <v>1.4597</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K159">
-        <v>1.4597</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L159" t="s">
         <v>15</v>
@@ -7455,10 +7452,10 @@
         <v>159</v>
       </c>
       <c r="C160">
-        <v>1362</v>
+        <v>1193</v>
       </c>
       <c r="D160">
-        <v>1670</v>
+        <v>1681</v>
       </c>
       <c r="E160">
         <v>52</v>
@@ -7467,19 +7464,19 @@
         <v>2123.72</v>
       </c>
       <c r="G160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H160">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="I160">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J160">
-        <v>0.8947000000000001</v>
+        <v>3.7199</v>
       </c>
       <c r="K160">
-        <v>0.8947000000000001</v>
+        <v>1.4126</v>
       </c>
       <c r="L160" t="s">
         <v>15</v>
@@ -7499,10 +7496,10 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>1193</v>
+        <v>1445</v>
       </c>
       <c r="D161">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="E161">
         <v>52</v>
@@ -7511,19 +7508,19 @@
         <v>2123.72</v>
       </c>
       <c r="G161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H161">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="I161">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J161">
-        <v>3.7199</v>
+        <v>1.4597</v>
       </c>
       <c r="K161">
-        <v>1.4126</v>
+        <v>1.4597</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -7587,7 +7584,7 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D163">
         <v>1730</v>
@@ -7763,31 +7760,31 @@
         <v>166</v>
       </c>
       <c r="C167">
-        <v>1191</v>
+        <v>1786</v>
       </c>
       <c r="D167">
-        <v>1741</v>
+        <v>1734</v>
       </c>
       <c r="E167">
+        <v>50</v>
+      </c>
+      <c r="F167">
+        <v>1963.5</v>
+      </c>
+      <c r="G167">
+        <v>2</v>
+      </c>
+      <c r="H167">
         <v>52</v>
       </c>
-      <c r="F167">
-        <v>2123.72</v>
-      </c>
-      <c r="G167">
-        <v>3</v>
-      </c>
-      <c r="H167">
-        <v>73</v>
-      </c>
       <c r="I167">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J167">
-        <v>3.4374</v>
+        <v>2.6483</v>
       </c>
       <c r="K167">
-        <v>1.8835</v>
+        <v>1.3242</v>
       </c>
       <c r="L167" t="s">
         <v>15</v>
@@ -7807,10 +7804,10 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>1786</v>
+        <v>1874</v>
       </c>
       <c r="D168">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="E168">
         <v>50</v>
@@ -7819,19 +7816,19 @@
         <v>1963.5</v>
       </c>
       <c r="G168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H168">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I168">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="J168">
-        <v>2.6483</v>
+        <v>4.1762</v>
       </c>
       <c r="K168">
-        <v>1.3242</v>
+        <v>4.1762</v>
       </c>
       <c r="L168" t="s">
         <v>15</v>
@@ -7851,31 +7848,31 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>1874</v>
+        <v>851</v>
       </c>
       <c r="D169">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E169">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F169">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="I169">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="J169">
-        <v>4.1762</v>
+        <v>0</v>
       </c>
       <c r="K169">
-        <v>4.1762</v>
+        <v>0</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7895,10 +7892,10 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>851</v>
+        <v>942</v>
       </c>
       <c r="D170">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="E170">
         <v>52</v>
@@ -7907,19 +7904,19 @@
         <v>2123.72</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>0.7534</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>0.7534</v>
       </c>
       <c r="L170" t="s">
         <v>15</v>
@@ -7939,10 +7936,10 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>942</v>
+        <v>1280</v>
       </c>
       <c r="D171">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E171">
         <v>52</v>
@@ -7951,19 +7948,19 @@
         <v>2123.72</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I171">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J171">
-        <v>0.7534</v>
+        <v>0</v>
       </c>
       <c r="K171">
-        <v>0.7534</v>
+        <v>0</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -7983,10 +7980,10 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>1280</v>
+        <v>1363</v>
       </c>
       <c r="D172">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E172">
         <v>52</v>
@@ -7995,19 +7992,19 @@
         <v>2123.72</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I172">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>3.4374</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>1.5068</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8027,10 +8024,10 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>1363</v>
+        <v>1443</v>
       </c>
       <c r="D173">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="E173">
         <v>52</v>
@@ -8039,19 +8036,19 @@
         <v>2123.72</v>
       </c>
       <c r="G173">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="I173">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J173">
-        <v>3.4374</v>
+        <v>2.7311</v>
       </c>
       <c r="K173">
-        <v>1.5068</v>
+        <v>2.7311</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -8071,31 +8068,31 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>1443</v>
+        <v>1532</v>
       </c>
       <c r="D174">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="E174">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F174">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H174">
         <v>58</v>
       </c>
       <c r="I174">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J174">
-        <v>2.7311</v>
+        <v>3.2052</v>
       </c>
       <c r="K174">
-        <v>2.7311</v>
+        <v>1.7131</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8115,31 +8112,31 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1532</v>
+        <v>1618</v>
       </c>
       <c r="D175">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="E175">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F175">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H175">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="I175">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J175">
-        <v>3.2052</v>
+        <v>2.1189</v>
       </c>
       <c r="K175">
-        <v>1.7131</v>
+        <v>2.1189</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8159,10 +8156,10 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>1618</v>
+        <v>1692</v>
       </c>
       <c r="D176">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="E176">
         <v>52</v>
@@ -8171,19 +8168,19 @@
         <v>2123.72</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I176">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J176">
-        <v>2.1189</v>
+        <v>0</v>
       </c>
       <c r="K176">
-        <v>2.1189</v>
+        <v>0</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8203,10 +8200,10 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>1692</v>
+        <v>1190</v>
       </c>
       <c r="D177">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="E177">
         <v>52</v>
@@ -8215,19 +8212,19 @@
         <v>2123.72</v>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I177">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>2.6369</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>1.8835</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -8247,31 +8244,31 @@
         <v>177</v>
       </c>
       <c r="C178">
-        <v>1621</v>
+        <v>683</v>
       </c>
       <c r="D178">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E178">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F178">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H178">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I178">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J178">
-        <v>2.1</v>
+        <v>1.6481</v>
       </c>
       <c r="K178">
-        <v>1.2158</v>
+        <v>1.6481</v>
       </c>
       <c r="L178" t="s">
         <v>15</v>
@@ -8291,31 +8288,31 @@
         <v>178</v>
       </c>
       <c r="C179">
-        <v>683</v>
+        <v>1875</v>
       </c>
       <c r="D179">
         <v>1790</v>
       </c>
       <c r="E179">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F179">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G179">
         <v>1</v>
       </c>
       <c r="H179">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I179">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J179">
-        <v>1.6481</v>
+        <v>1.3242</v>
       </c>
       <c r="K179">
-        <v>1.6481</v>
+        <v>1.3242</v>
       </c>
       <c r="L179" t="s">
         <v>15</v>
@@ -8335,7 +8332,7 @@
         <v>179</v>
       </c>
       <c r="C180">
-        <v>1875</v>
+        <v>1960</v>
       </c>
       <c r="D180">
         <v>1790</v>
@@ -8347,19 +8344,19 @@
         <v>1963.5</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H180">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="I180">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J180">
-        <v>1.3242</v>
+        <v>4.1253</v>
       </c>
       <c r="K180">
-        <v>1.3242</v>
+        <v>2.19</v>
       </c>
       <c r="L180" t="s">
         <v>15</v>
@@ -8379,31 +8376,31 @@
         <v>180</v>
       </c>
       <c r="C181">
-        <v>1960</v>
+        <v>762</v>
       </c>
       <c r="D181">
         <v>1790</v>
       </c>
       <c r="E181">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F181">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H181">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="I181">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J181">
-        <v>4.1253</v>
+        <v>1.9306</v>
       </c>
       <c r="K181">
-        <v>2.19</v>
+        <v>1.9306</v>
       </c>
       <c r="L181" t="s">
         <v>15</v>
@@ -8423,31 +8420,31 @@
         <v>181</v>
       </c>
       <c r="C182">
-        <v>762</v>
+        <v>850</v>
       </c>
       <c r="D182">
         <v>1790</v>
       </c>
       <c r="E182">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F182">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G182">
         <v>1</v>
       </c>
       <c r="H182">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="I182">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="J182">
-        <v>1.9306</v>
+        <v>3.7179</v>
       </c>
       <c r="K182">
-        <v>1.9306</v>
+        <v>3.7179</v>
       </c>
       <c r="L182" t="s">
         <v>15</v>
@@ -8467,31 +8464,31 @@
         <v>182</v>
       </c>
       <c r="C183">
-        <v>850</v>
+        <v>939</v>
       </c>
       <c r="D183">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="E183">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F183">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G183">
         <v>1</v>
       </c>
       <c r="H183">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="I183">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="J183">
-        <v>3.7179</v>
+        <v>1.8789</v>
       </c>
       <c r="K183">
-        <v>3.7179</v>
+        <v>1.8789</v>
       </c>
       <c r="L183" t="s">
         <v>15</v>
@@ -8511,31 +8508,31 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>939</v>
+        <v>1024</v>
       </c>
       <c r="D184">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E184">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F184">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I184">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J184">
-        <v>1.8789</v>
+        <v>0</v>
       </c>
       <c r="K184">
-        <v>1.8789</v>
+        <v>0</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8555,10 +8552,10 @@
         <v>184</v>
       </c>
       <c r="C185">
-        <v>1024</v>
+        <v>1108</v>
       </c>
       <c r="D185">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="E185">
         <v>52</v>
@@ -8567,19 +8564,19 @@
         <v>2123.72</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I185">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>4.0024</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>2.9665</v>
       </c>
       <c r="L185" t="s">
         <v>15</v>
@@ -8599,10 +8596,10 @@
         <v>185</v>
       </c>
       <c r="C186">
-        <v>1108</v>
+        <v>1194</v>
       </c>
       <c r="D186">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="E186">
         <v>52</v>
@@ -8611,19 +8608,19 @@
         <v>2123.72</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I186">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J186">
-        <v>4.0024</v>
+        <v>0</v>
       </c>
       <c r="K186">
-        <v>2.9665</v>
+        <v>0</v>
       </c>
       <c r="L186" t="s">
         <v>15</v>
@@ -8643,10 +8640,10 @@
         <v>186</v>
       </c>
       <c r="C187">
-        <v>1194</v>
+        <v>1279</v>
       </c>
       <c r="D187">
-        <v>1791</v>
+        <v>1802</v>
       </c>
       <c r="E187">
         <v>52</v>
@@ -8687,31 +8684,31 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>1279</v>
+        <v>1368</v>
       </c>
       <c r="D188">
-        <v>1802</v>
+        <v>1791</v>
       </c>
       <c r="E188">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F188">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I188">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>1.1714</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>1.1714</v>
       </c>
       <c r="L188" t="s">
         <v>15</v>
@@ -8731,10 +8728,10 @@
         <v>188</v>
       </c>
       <c r="C189">
-        <v>1368</v>
+        <v>1538</v>
       </c>
       <c r="D189">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E189">
         <v>50</v>
@@ -8746,16 +8743,16 @@
         <v>1</v>
       </c>
       <c r="H189">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I189">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J189">
-        <v>1.1714</v>
+        <v>2.19</v>
       </c>
       <c r="K189">
-        <v>1.1714</v>
+        <v>2.19</v>
       </c>
       <c r="L189" t="s">
         <v>15</v>
@@ -8775,10 +8772,10 @@
         <v>189</v>
       </c>
       <c r="C190">
-        <v>1538</v>
+        <v>1705</v>
       </c>
       <c r="D190">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E190">
         <v>50</v>
@@ -8787,19 +8784,19 @@
         <v>1963.5</v>
       </c>
       <c r="G190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="I190">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J190">
-        <v>2.19</v>
+        <v>3.1576</v>
       </c>
       <c r="K190">
-        <v>2.19</v>
+        <v>1.8335</v>
       </c>
       <c r="L190" t="s">
         <v>15</v>
@@ -8819,7 +8816,7 @@
         <v>190</v>
       </c>
       <c r="C191">
-        <v>1705</v>
+        <v>1790</v>
       </c>
       <c r="D191">
         <v>1791</v>
@@ -8834,16 +8831,16 @@
         <v>2</v>
       </c>
       <c r="H191">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I191">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J191">
-        <v>3.1576</v>
+        <v>3.4123</v>
       </c>
       <c r="K191">
-        <v>1.8335</v>
+        <v>2.4955</v>
       </c>
       <c r="L191" t="s">
         <v>15</v>
@@ -8863,31 +8860,31 @@
         <v>191</v>
       </c>
       <c r="C192">
-        <v>1790</v>
+        <v>1449</v>
       </c>
       <c r="D192">
         <v>1791</v>
       </c>
       <c r="E192">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F192">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G192">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H192">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I192">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J192">
-        <v>3.4123</v>
+        <v>3.371</v>
       </c>
       <c r="K192">
-        <v>2.4955</v>
+        <v>3.371</v>
       </c>
       <c r="L192" t="s">
         <v>15</v>
@@ -8907,31 +8904,31 @@
         <v>192</v>
       </c>
       <c r="C193">
-        <v>1449</v>
+        <v>1630</v>
       </c>
       <c r="D193">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E193">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F193">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H193">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="I193">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="J193">
-        <v>3.371</v>
+        <v>1.7893</v>
       </c>
       <c r="K193">
-        <v>3.371</v>
+        <v>1.0359</v>
       </c>
       <c r="L193" t="s">
         <v>15</v>
@@ -9083,10 +9080,10 @@
         <v>196</v>
       </c>
       <c r="C197">
-        <v>1708</v>
+        <v>1019</v>
       </c>
       <c r="D197">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="E197">
         <v>52</v>
@@ -9098,16 +9095,16 @@
         <v>2</v>
       </c>
       <c r="H197">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I197">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J197">
-        <v>3.6257</v>
+        <v>3.4845</v>
       </c>
       <c r="K197">
-        <v>1.8835</v>
+        <v>1.9777</v>
       </c>
       <c r="L197" t="s">
         <v>15</v>
@@ -9127,31 +9124,31 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>1796</v>
+        <v>1708</v>
       </c>
       <c r="D198">
         <v>1848</v>
       </c>
       <c r="E198">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F198">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H198">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I198">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J198">
-        <v>1.3263</v>
+        <v>3.6257</v>
       </c>
       <c r="K198">
-        <v>1.3263</v>
+        <v>1.8835</v>
       </c>
       <c r="L198" t="s">
         <v>15</v>
@@ -9171,31 +9168,31 @@
         <v>198</v>
       </c>
       <c r="C199">
-        <v>1880</v>
+        <v>1796</v>
       </c>
       <c r="D199">
         <v>1848</v>
       </c>
       <c r="E199">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F199">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G199">
         <v>1</v>
       </c>
       <c r="H199">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="I199">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="J199">
-        <v>3.7688</v>
+        <v>1.3263</v>
       </c>
       <c r="K199">
-        <v>3.7688</v>
+        <v>1.3263</v>
       </c>
       <c r="L199" t="s">
         <v>15</v>
@@ -9215,10 +9212,10 @@
         <v>199</v>
       </c>
       <c r="C200">
-        <v>853</v>
+        <v>1880</v>
       </c>
       <c r="D200">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="E200">
         <v>50</v>
@@ -9227,19 +9224,19 @@
         <v>1963.5</v>
       </c>
       <c r="G200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H200">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I200">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J200">
-        <v>3.5141</v>
+        <v>3.7688</v>
       </c>
       <c r="K200">
-        <v>2.2409</v>
+        <v>3.7688</v>
       </c>
       <c r="L200" t="s">
         <v>15</v>
@@ -9259,31 +9256,31 @@
         <v>200</v>
       </c>
       <c r="C201">
-        <v>937</v>
+        <v>853</v>
       </c>
       <c r="D201">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="E201">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F201">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I201">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J201">
-        <v>0</v>
+        <v>3.5141</v>
       </c>
       <c r="K201">
-        <v>0</v>
+        <v>2.2409</v>
       </c>
       <c r="L201" t="s">
         <v>15</v>
@@ -9303,7 +9300,7 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>1018</v>
+        <v>937</v>
       </c>
       <c r="D202">
         <v>1849</v>
@@ -9315,19 +9312,19 @@
         <v>2123.72</v>
       </c>
       <c r="G202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="I202">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J202">
-        <v>3.4845</v>
+        <v>0</v>
       </c>
       <c r="K202">
-        <v>1.9777</v>
+        <v>0</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -9655,10 +9652,10 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>1196</v>
+        <v>936</v>
       </c>
       <c r="D210">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="E210">
         <v>52</v>
@@ -9667,19 +9664,19 @@
         <v>2123.72</v>
       </c>
       <c r="G210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H210">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I210">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J210">
-        <v>3.4374</v>
+        <v>2.8252</v>
       </c>
       <c r="K210">
-        <v>2.684</v>
+        <v>2.8252</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9699,31 +9696,31 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>677</v>
+        <v>1196</v>
       </c>
       <c r="D211">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="E211">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F211">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G211">
         <v>2</v>
       </c>
       <c r="H211">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I211">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J211">
-        <v>3.5651</v>
+        <v>3.4374</v>
       </c>
       <c r="K211">
-        <v>2.7502</v>
+        <v>2.684</v>
       </c>
       <c r="L211" t="s">
         <v>15</v>
@@ -9743,31 +9740,31 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>758</v>
+        <v>677</v>
       </c>
       <c r="D212">
-        <v>1915</v>
+        <v>1907</v>
       </c>
       <c r="E212">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F212">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H212">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="I212">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="J212">
-        <v>1.3655</v>
+        <v>3.5651</v>
       </c>
       <c r="K212">
-        <v>1.3655</v>
+        <v>2.7502</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9787,10 +9784,10 @@
         <v>212</v>
       </c>
       <c r="C213">
-        <v>845</v>
+        <v>758</v>
       </c>
       <c r="D213">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="E213">
         <v>52</v>
@@ -9799,19 +9796,19 @@
         <v>2123.72</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I213">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J213">
-        <v>0</v>
+        <v>1.3655</v>
       </c>
       <c r="K213">
-        <v>0</v>
+        <v>1.3655</v>
       </c>
       <c r="L213" t="s">
         <v>15</v>
@@ -9831,10 +9828,10 @@
         <v>213</v>
       </c>
       <c r="C214">
-        <v>1107</v>
+        <v>845</v>
       </c>
       <c r="D214">
-        <v>1913</v>
+        <v>1918</v>
       </c>
       <c r="E214">
         <v>52</v>
@@ -10315,10 +10312,10 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>920</v>
+        <v>1111</v>
       </c>
       <c r="D225">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="E225">
         <v>52</v>
@@ -10359,16 +10356,16 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>673</v>
+        <v>939</v>
       </c>
       <c r="D226">
-        <v>1965</v>
+        <v>1978</v>
       </c>
       <c r="E226">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F226">
-        <v>1809.56</v>
+        <v>1134.11</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -10403,10 +10400,10 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>758</v>
+        <v>1701</v>
       </c>
       <c r="D227">
-        <v>1953</v>
+        <v>1948</v>
       </c>
       <c r="E227">
         <v>52</v>
@@ -10447,31 +10444,31 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>1890</v>
+        <v>1280</v>
       </c>
       <c r="D228">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="E228">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F228">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H228">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="I228">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="J228">
-        <v>5.6532</v>
+        <v>3.7199</v>
       </c>
       <c r="K228">
-        <v>5.6532</v>
+        <v>2.4485</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -10491,16 +10488,16 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>1973</v>
+        <v>673</v>
       </c>
       <c r="D229">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E229">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F229">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -10535,10 +10532,10 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>842</v>
+        <v>758</v>
       </c>
       <c r="D230">
-        <v>1962</v>
+        <v>1953</v>
       </c>
       <c r="E230">
         <v>52</v>
@@ -10547,19 +10544,19 @@
         <v>2123.72</v>
       </c>
       <c r="G230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H230">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="I230">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J230">
-        <v>3.1548</v>
+        <v>0</v>
       </c>
       <c r="K230">
-        <v>2.166</v>
+        <v>0</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10579,31 +10576,31 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>1020</v>
+        <v>1890</v>
       </c>
       <c r="D231">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E231">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F231">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G231">
         <v>1</v>
       </c>
       <c r="H231">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="I231">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="J231">
-        <v>1.083</v>
+        <v>5.6532</v>
       </c>
       <c r="K231">
-        <v>1.083</v>
+        <v>5.6532</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10623,31 +10620,31 @@
         <v>231</v>
       </c>
       <c r="C232">
-        <v>1368</v>
+        <v>1973</v>
       </c>
       <c r="D232">
         <v>1966</v>
       </c>
       <c r="E232">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F232">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="I232">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="J232">
-        <v>4.3791</v>
+        <v>0</v>
       </c>
       <c r="K232">
-        <v>4.3791</v>
+        <v>0</v>
       </c>
       <c r="L232" t="s">
         <v>15</v>
@@ -10667,10 +10664,10 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>1455</v>
+        <v>842</v>
       </c>
       <c r="D233">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="E233">
         <v>52</v>
@@ -10679,19 +10676,19 @@
         <v>2123.72</v>
       </c>
       <c r="G233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H233">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="I233">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="J233">
-        <v>4.9442</v>
+        <v>3.1548</v>
       </c>
       <c r="K233">
-        <v>4.9442</v>
+        <v>2.166</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10711,31 +10708,31 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>1544</v>
+        <v>1020</v>
       </c>
       <c r="D234">
         <v>1966</v>
       </c>
       <c r="E234">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F234">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G234">
         <v>1</v>
       </c>
       <c r="H234">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="I234">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="J234">
-        <v>6.4681</v>
+        <v>1.083</v>
       </c>
       <c r="K234">
-        <v>6.4681</v>
+        <v>1.083</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10755,7 +10752,7 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>1629</v>
+        <v>1368</v>
       </c>
       <c r="D235">
         <v>1966</v>
@@ -10767,19 +10764,19 @@
         <v>2123.72</v>
       </c>
       <c r="G235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H235">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I235">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J235">
-        <v>3.767</v>
+        <v>4.3791</v>
       </c>
       <c r="K235">
-        <v>1.9306</v>
+        <v>4.3791</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10799,7 +10796,7 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>1803</v>
+        <v>1455</v>
       </c>
       <c r="D236">
         <v>1966</v>
@@ -10814,16 +10811,16 @@
         <v>1</v>
       </c>
       <c r="H236">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="I236">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="J236">
-        <v>7.0631</v>
+        <v>4.9442</v>
       </c>
       <c r="K236">
-        <v>7.0631</v>
+        <v>4.9442</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10843,31 +10840,31 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1195</v>
+        <v>1544</v>
       </c>
       <c r="D237">
         <v>1966</v>
       </c>
       <c r="E237">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F237">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G237">
         <v>1</v>
       </c>
       <c r="H237">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="I237">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="J237">
-        <v>4.3104</v>
+        <v>6.4681</v>
       </c>
       <c r="K237">
-        <v>4.3104</v>
+        <v>6.4681</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10887,10 +10884,10 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1281</v>
+        <v>1629</v>
       </c>
       <c r="D238">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E238">
         <v>52</v>
@@ -10902,16 +10899,16 @@
         <v>2</v>
       </c>
       <c r="H238">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I238">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="J238">
-        <v>3.6728</v>
+        <v>3.767</v>
       </c>
       <c r="K238">
-        <v>2.4485</v>
+        <v>1.9306</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10931,10 +10928,10 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>1109</v>
+        <v>1803</v>
       </c>
       <c r="D239">
-        <v>1957</v>
+        <v>1966</v>
       </c>
       <c r="E239">
         <v>52</v>
@@ -10943,19 +10940,19 @@
         <v>2123.72</v>
       </c>
       <c r="G239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H239">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="I239">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="J239">
-        <v>3.8612</v>
+        <v>7.0631</v>
       </c>
       <c r="K239">
-        <v>2.0718</v>
+        <v>7.0631</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -10975,31 +10972,31 @@
         <v>239</v>
       </c>
       <c r="C240">
-        <v>1695</v>
+        <v>1195</v>
       </c>
       <c r="D240">
-        <v>1976</v>
+        <v>1966</v>
       </c>
       <c r="E240">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F240">
-        <v>1385.44</v>
+        <v>1809.56</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I240">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J240">
-        <v>0</v>
+        <v>4.3104</v>
       </c>
       <c r="K240">
-        <v>0</v>
+        <v>4.3104</v>
       </c>
       <c r="L240" t="s">
         <v>15</v>
@@ -11063,10 +11060,10 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>1984</v>
+        <v>1542</v>
       </c>
       <c r="D242">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="E242">
         <v>52</v>
@@ -11075,19 +11072,19 @@
         <v>2123.72</v>
       </c>
       <c r="G242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H242">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I242">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J242">
-        <v>1.8835</v>
+        <v>0</v>
       </c>
       <c r="K242">
-        <v>1.8835</v>
+        <v>0</v>
       </c>
       <c r="L242" t="s">
         <v>15</v>
@@ -11107,31 +11104,31 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1106</v>
+        <v>1370</v>
       </c>
       <c r="D243">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E243">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F243">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I243">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J243">
-        <v>2.8252</v>
+        <v>0</v>
       </c>
       <c r="K243">
-        <v>2.8252</v>
+        <v>0</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11151,16 +11148,16 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>1520</v>
+        <v>759</v>
       </c>
       <c r="D244">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="E244">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F244">
-        <v>1520.53</v>
+        <v>1661.9</v>
       </c>
       <c r="G244">
         <v>0</v>
@@ -11195,10 +11192,10 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>1899</v>
+        <v>1724</v>
       </c>
       <c r="D245">
-        <v>2024</v>
+        <v>2031</v>
       </c>
       <c r="E245">
         <v>52</v>
@@ -11207,19 +11204,19 @@
         <v>2123.72</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I245">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J245">
-        <v>0</v>
+        <v>3.5315</v>
       </c>
       <c r="K245">
-        <v>0</v>
+        <v>2.3073</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -11239,16 +11236,16 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>667</v>
+        <v>1812</v>
       </c>
       <c r="D246">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="E246">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F246">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -11283,10 +11280,10 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>1018</v>
+        <v>1984</v>
       </c>
       <c r="D247">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="E247">
         <v>52</v>
@@ -11295,19 +11292,19 @@
         <v>2123.72</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I247">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>1.8835</v>
       </c>
       <c r="K247">
-        <v>0</v>
+        <v>1.8835</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11327,10 +11324,10 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1372</v>
+        <v>1106</v>
       </c>
       <c r="D248">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E248">
         <v>52</v>
@@ -11339,19 +11336,19 @@
         <v>2123.72</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I248">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>2.8252</v>
       </c>
       <c r="K248">
-        <v>0</v>
+        <v>2.8252</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11371,10 +11368,10 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>1454</v>
+        <v>1899</v>
       </c>
       <c r="D249">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="E249">
         <v>52</v>
@@ -11383,19 +11380,19 @@
         <v>2123.72</v>
       </c>
       <c r="G249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I249">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J249">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="K249">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11415,31 +11412,31 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>1723</v>
+        <v>667</v>
       </c>
       <c r="D250">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E250">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F250">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G250">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I250">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J250">
-        <v>3.5315</v>
+        <v>0</v>
       </c>
       <c r="K250">
-        <v>2.3073</v>
+        <v>0</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11459,10 +11456,10 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>1811</v>
+        <v>1018</v>
       </c>
       <c r="D251">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E251">
         <v>52</v>
@@ -11547,10 +11544,10 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>760</v>
+        <v>1288</v>
       </c>
       <c r="D253">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="E253">
         <v>52</v>
@@ -11591,10 +11588,10 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>1288</v>
+        <v>1184</v>
       </c>
       <c r="D254">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="E254">
         <v>52</v>
@@ -11635,10 +11632,10 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1184</v>
+        <v>845</v>
       </c>
       <c r="D255">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="E255">
         <v>52</v>
@@ -11679,16 +11676,16 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>845</v>
+        <v>1692</v>
       </c>
       <c r="D256">
-        <v>2037</v>
+        <v>1210</v>
       </c>
       <c r="E256">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F256">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G256">
         <v>0</v>
@@ -11709,10 +11706,10 @@
         <v>15</v>
       </c>
       <c r="M256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N256">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -11723,10 +11720,10 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>943</v>
+        <v>1455</v>
       </c>
       <c r="D257">
-        <v>1992</v>
+        <v>2027</v>
       </c>
       <c r="E257">
         <v>52</v>
@@ -11738,16 +11735,16 @@
         <v>1</v>
       </c>
       <c r="H257">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="I257">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="J257">
-        <v>7.6281</v>
+        <v>1.1301</v>
       </c>
       <c r="K257">
-        <v>7.6281</v>
+        <v>1.1301</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
@@ -11788,40 +11785,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>27</v>
-      </c>
-      <c r="M1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -11832,10 +11829,10 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>1.7786</v>
+        <v>1.6496</v>
       </c>
       <c r="D2">
-        <v>13.5479</v>
+        <v>7.3339</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11844,7 +11841,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -11853,16 +11850,16 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Images_BGA/Results/Reports/PCBA2_06_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_06_inspection_report.xlsx
@@ -500,16 +500,16 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1685</v>
+        <v>1574</v>
       </c>
       <c r="D2">
-        <v>1167</v>
+        <v>1187</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F2">
-        <v>1385.44</v>
+        <v>2123.72</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -544,16 +544,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1626</v>
+        <v>1131</v>
       </c>
       <c r="D3">
-        <v>1178</v>
+        <v>1204</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F3">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1951</v>
+        <v>1195</v>
       </c>
       <c r="D4">
-        <v>1190</v>
+        <v>1210</v>
       </c>
       <c r="E4">
         <v>46</v>
@@ -632,16 +632,16 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>768</v>
+        <v>1274</v>
       </c>
       <c r="D5">
-        <v>1192</v>
+        <v>1210</v>
       </c>
       <c r="E5">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1820</v>
+        <v>1353</v>
       </c>
       <c r="D6">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F6">
-        <v>1256.64</v>
+        <v>1661.9</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="I6">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>6.0479</v>
+        <v>0.9628</v>
       </c>
       <c r="K6">
-        <v>6.0479</v>
+        <v>0.9628</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -720,31 +720,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>945</v>
+        <v>1432</v>
       </c>
       <c r="D7">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F7">
-        <v>1385.44</v>
+        <v>1661.9</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1.9857</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1.0229</v>
       </c>
       <c r="L7" t="s">
         <v>15</v>
@@ -764,31 +764,31 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1898</v>
+        <v>1511</v>
       </c>
       <c r="D8">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>1385.44</v>
+        <v>1809.56</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>6.4239</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>6.4239</v>
+        <v>0</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -808,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1117</v>
+        <v>1676</v>
       </c>
       <c r="D9">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F9">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.8842</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.8842</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -852,31 +852,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1195</v>
+        <v>1748</v>
       </c>
       <c r="D10">
-        <v>1210</v>
+        <v>1201</v>
       </c>
       <c r="E10">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F10">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1.4126</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1.4126</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -896,31 +896,31 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1274</v>
+        <v>1831</v>
       </c>
       <c r="D11">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="E11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F11">
-        <v>1661.9</v>
+        <v>1385.44</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>11.4043</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>6.1352</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -940,31 +940,31 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>1353</v>
+        <v>1907</v>
       </c>
       <c r="D12">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="E12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F12">
-        <v>1661.9</v>
+        <v>1385.44</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="J12">
-        <v>0.9628</v>
+        <v>6.6405</v>
       </c>
       <c r="K12">
-        <v>0.9628</v>
+        <v>5.4856</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -984,31 +984,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1431</v>
+        <v>880</v>
       </c>
       <c r="D13">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F13">
-        <v>1520.53</v>
+        <v>1661.9</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>2.6307</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>1.5784</v>
+        <v>0</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1028,31 +1028,31 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>1511</v>
+        <v>1038</v>
       </c>
       <c r="D14">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F14">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1.3238</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1.3238</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1072,31 +1072,31 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>880</v>
+        <v>716</v>
       </c>
       <c r="D15">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F15">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2.1552</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2.1552</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1116,10 +1116,10 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1038</v>
+        <v>791</v>
       </c>
       <c r="D16">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="E16">
         <v>46</v>
@@ -1128,19 +1128,19 @@
         <v>1661.9</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>1.3238</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>1.3238</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1160,31 +1160,31 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>719</v>
+        <v>959</v>
       </c>
       <c r="D17">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="E17">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F17">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="I17">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J17">
-        <v>4.3926</v>
+        <v>1.1301</v>
       </c>
       <c r="K17">
-        <v>2.4671</v>
+        <v>1.1301</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -1204,31 +1204,31 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>719</v>
+        <v>1909</v>
       </c>
       <c r="D18">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="E18">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>1385.44</v>
+        <v>1520.53</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="I18">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="J18">
-        <v>3.9699</v>
+        <v>2.2361</v>
       </c>
       <c r="K18">
-        <v>3.9699</v>
+        <v>1.1838</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -1248,31 +1248,31 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>790</v>
+        <v>1434</v>
       </c>
       <c r="D19">
-        <v>1243</v>
+        <v>1259</v>
       </c>
       <c r="E19">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F19">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2.4671</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2.4671</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1292,31 +1292,31 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>1434</v>
+        <v>1592</v>
       </c>
       <c r="D20">
         <v>1259</v>
       </c>
       <c r="E20">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F20">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I20">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="J20">
-        <v>2.4671</v>
+        <v>1.2158</v>
       </c>
       <c r="K20">
-        <v>2.4671</v>
+        <v>1.2158</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1336,10 +1336,10 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>1592</v>
+        <v>1831</v>
       </c>
       <c r="D21">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E21">
         <v>48</v>
@@ -1348,19 +1348,19 @@
         <v>1809.56</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1.2158</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1.2158</v>
+        <v>0</v>
       </c>
       <c r="L21" t="s">
         <v>15</v>
@@ -1380,10 +1380,10 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>1829</v>
+        <v>716</v>
       </c>
       <c r="D22">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E22">
         <v>46</v>
@@ -1392,19 +1392,19 @@
         <v>1661.9</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I22">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J22">
-        <v>2.2264</v>
+        <v>3.3095</v>
       </c>
       <c r="K22">
-        <v>1.2034</v>
+        <v>3.3095</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1424,31 +1424,31 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>1926</v>
+        <v>873</v>
       </c>
       <c r="D23">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="E23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F23">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1.6848</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1.6848</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1468,31 +1468,31 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>876</v>
+        <v>1031</v>
       </c>
       <c r="D24">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="E24">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F24">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1.6848</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>1.6848</v>
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1512,16 +1512,16 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>1033</v>
+        <v>1116</v>
       </c>
       <c r="D25">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F25">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1556,16 +1556,16 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>1108</v>
+        <v>1195</v>
       </c>
       <c r="D26">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="E26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F26">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1195</v>
+        <v>1275</v>
       </c>
       <c r="D27">
         <v>1260</v>
@@ -1612,19 +1612,19 @@
         <v>1661.9</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>0.9628</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>0.9628</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -1644,7 +1644,7 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>1275</v>
+        <v>1355</v>
       </c>
       <c r="D28">
         <v>1260</v>
@@ -1659,16 +1659,16 @@
         <v>1</v>
       </c>
       <c r="H28">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I28">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J28">
-        <v>0.9628</v>
+        <v>1.0831</v>
       </c>
       <c r="K28">
-        <v>0.9628</v>
+        <v>1.0831</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -1688,7 +1688,7 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>1355</v>
+        <v>1514</v>
       </c>
       <c r="D29">
         <v>1260</v>
@@ -1700,19 +1700,19 @@
         <v>1661.9</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>1.0831</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>1.0831</v>
+        <v>0</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1732,16 +1732,16 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>1514</v>
+        <v>1737</v>
       </c>
       <c r="D30">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E30">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F30">
-        <v>1661.9</v>
+        <v>1385.44</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1776,31 +1776,31 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1761</v>
+        <v>798</v>
       </c>
       <c r="D31">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E31">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F31">
-        <v>1385.44</v>
+        <v>1661.9</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1.6601</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1.6601</v>
+        <v>0</v>
       </c>
       <c r="L31" t="s">
         <v>15</v>
@@ -1820,16 +1820,16 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>1710</v>
+        <v>949</v>
       </c>
       <c r="D32">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="E32">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F32">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1864,31 +1864,31 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>949</v>
+        <v>1671</v>
       </c>
       <c r="D33">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="E33">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F33">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>5.933</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>5.0383</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -1908,16 +1908,16 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>1930</v>
+        <v>1754</v>
       </c>
       <c r="D34">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E34">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F34">
-        <v>1809.56</v>
+        <v>1520.53</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1952,16 +1952,16 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>1754</v>
+        <v>1433</v>
       </c>
       <c r="D35">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E35">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F35">
-        <v>1520.53</v>
+        <v>1661.9</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1996,31 +1996,31 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>1433</v>
+        <v>1515</v>
       </c>
       <c r="D36">
         <v>1309</v>
       </c>
       <c r="E36">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F36">
-        <v>1520.53</v>
+        <v>1809.56</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>3.1499</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1.6026</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2040,31 +2040,31 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>1515</v>
+        <v>1594</v>
       </c>
       <c r="D37">
         <v>1309</v>
       </c>
       <c r="E37">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F37">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>3.1499</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>1.6026</v>
+        <v>0</v>
       </c>
       <c r="L37" t="s">
         <v>15</v>
@@ -2084,7 +2084,7 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>1594</v>
+        <v>1674</v>
       </c>
       <c r="D38">
         <v>1309</v>
@@ -2096,19 +2096,19 @@
         <v>1661.9</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1.4441</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1.4441</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2128,31 +2128,31 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1674</v>
+        <v>1835</v>
       </c>
       <c r="D39">
         <v>1309</v>
       </c>
       <c r="E39">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F39">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1.4441</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>1.4441</v>
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2172,31 +2172,31 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>1827</v>
+        <v>709</v>
       </c>
       <c r="D40">
         <v>1310</v>
       </c>
       <c r="E40">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F40">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1.2158</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1.2158</v>
       </c>
       <c r="L40" t="s">
         <v>15</v>
@@ -2216,31 +2216,31 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>708</v>
+        <v>792</v>
       </c>
       <c r="D41">
         <v>1308</v>
       </c>
       <c r="E41">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F41">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>1.3184</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1.3184</v>
+        <v>0</v>
       </c>
       <c r="L41" t="s">
         <v>15</v>
@@ -2260,31 +2260,31 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>786</v>
+        <v>872</v>
       </c>
       <c r="D42">
         <v>1308</v>
       </c>
       <c r="E42">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F42">
-        <v>2123.72</v>
+        <v>1661.9</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1.745</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1.745</v>
       </c>
       <c r="L42" t="s">
         <v>15</v>
@@ -2304,10 +2304,10 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>872</v>
+        <v>954</v>
       </c>
       <c r="D43">
-        <v>1308</v>
+        <v>1297</v>
       </c>
       <c r="E43">
         <v>46</v>
@@ -2316,19 +2316,19 @@
         <v>1661.9</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>1.745</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>1.745</v>
+        <v>0</v>
       </c>
       <c r="L43" t="s">
         <v>15</v>
@@ -2348,7 +2348,7 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>956</v>
+        <v>1035</v>
       </c>
       <c r="D44">
         <v>1310</v>
@@ -2360,19 +2360,19 @@
         <v>1661.9</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>2.7077</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1.5645</v>
       </c>
       <c r="L44" t="s">
         <v>15</v>
@@ -2392,16 +2392,16 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D45">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="E45">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F45">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2436,7 +2436,7 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>1116</v>
+        <v>1195</v>
       </c>
       <c r="D46">
         <v>1310</v>
@@ -2480,16 +2480,16 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>1195</v>
+        <v>1274</v>
       </c>
       <c r="D47">
         <v>1310</v>
       </c>
       <c r="E47">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F47">
-        <v>1661.9</v>
+        <v>1520.53</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2524,7 +2524,7 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>1274</v>
+        <v>1355</v>
       </c>
       <c r="D48">
         <v>1310</v>
@@ -2568,16 +2568,16 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>1355</v>
+        <v>1921</v>
       </c>
       <c r="D49">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="E49">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F49">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2612,31 +2612,31 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>790</v>
+        <v>1927</v>
       </c>
       <c r="D50">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="E50">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F50">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I50">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J50">
-        <v>2.5421</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K50">
-        <v>1.3263</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2656,31 +2656,31 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>1927</v>
+        <v>1678</v>
       </c>
       <c r="D51">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="E51">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>2123.72</v>
+        <v>1520.53</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I51">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J51">
-        <v>0.8947000000000001</v>
+        <v>1.1838</v>
       </c>
       <c r="K51">
-        <v>0.8947000000000001</v>
+        <v>1.1838</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2700,31 +2700,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>1678</v>
+        <v>1763</v>
       </c>
       <c r="D52">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="E52">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F52">
-        <v>1520.53</v>
+        <v>1963.5</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I52">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="J52">
-        <v>1.1838</v>
+        <v>2.6993</v>
       </c>
       <c r="K52">
-        <v>1.1838</v>
+        <v>1.8844</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2744,31 +2744,31 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>1763</v>
+        <v>716</v>
       </c>
       <c r="D53">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F53">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="I53">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="J53">
-        <v>2.6993</v>
+        <v>5.4155</v>
       </c>
       <c r="K53">
-        <v>1.8844</v>
+        <v>5.4155</v>
       </c>
       <c r="L53" t="s">
         <v>15</v>
@@ -2788,31 +2788,31 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>716</v>
+        <v>873</v>
       </c>
       <c r="D54">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="E54">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F54">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="I54">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J54">
-        <v>5.4155</v>
+        <v>2.4315</v>
       </c>
       <c r="K54">
-        <v>5.4155</v>
+        <v>2.4315</v>
       </c>
       <c r="L54" t="s">
         <v>15</v>
@@ -2832,31 +2832,31 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>874</v>
+        <v>952</v>
       </c>
       <c r="D55">
         <v>1358</v>
       </c>
       <c r="E55">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F55">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I55">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J55">
-        <v>2.4315</v>
+        <v>3.3696</v>
       </c>
       <c r="K55">
-        <v>2.4315</v>
+        <v>1.2636</v>
       </c>
       <c r="L55" t="s">
         <v>15</v>
@@ -2876,10 +2876,10 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>952</v>
+        <v>1034</v>
       </c>
       <c r="D56">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E56">
         <v>46</v>
@@ -2888,19 +2888,19 @@
         <v>1661.9</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I56">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J56">
-        <v>3.3696</v>
+        <v>2.4069</v>
       </c>
       <c r="K56">
-        <v>1.2636</v>
+        <v>2.4069</v>
       </c>
       <c r="L56" t="s">
         <v>15</v>
@@ -2920,7 +2920,7 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>1034</v>
+        <v>1115</v>
       </c>
       <c r="D57">
         <v>1360</v>
@@ -2932,19 +2932,19 @@
         <v>1661.9</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I57">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J57">
-        <v>2.4069</v>
+        <v>2.7077</v>
       </c>
       <c r="K57">
-        <v>2.4069</v>
+        <v>1.5645</v>
       </c>
       <c r="L57" t="s">
         <v>15</v>
@@ -2964,31 +2964,31 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>1122</v>
+        <v>1195</v>
       </c>
       <c r="D58">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="E58">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F58">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>0.9677</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>0.9677</v>
+        <v>0</v>
       </c>
       <c r="L58" t="s">
         <v>15</v>
@@ -3008,7 +3008,7 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>1195</v>
+        <v>1274</v>
       </c>
       <c r="D59">
         <v>1360</v>
@@ -3020,19 +3020,19 @@
         <v>1661.9</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>0.9628</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>0.9628</v>
       </c>
       <c r="L59" t="s">
         <v>15</v>
@@ -3052,7 +3052,7 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>1274</v>
+        <v>1354</v>
       </c>
       <c r="D60">
         <v>1360</v>
@@ -3064,19 +3064,19 @@
         <v>1661.9</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>0.9628</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>0.9628</v>
+        <v>0</v>
       </c>
       <c r="L60" t="s">
         <v>15</v>
@@ -3096,16 +3096,16 @@
         <v>60</v>
       </c>
       <c r="C61">
-        <v>1354</v>
+        <v>1434</v>
       </c>
       <c r="D61">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="E61">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F61">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -3184,10 +3184,10 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>1595</v>
+        <v>1843</v>
       </c>
       <c r="D63">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="E63">
         <v>48</v>
@@ -3196,19 +3196,19 @@
         <v>1809.56</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="I63">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J63">
-        <v>3.8683</v>
+        <v>1.8789</v>
       </c>
       <c r="K63">
-        <v>2.2657</v>
+        <v>1.8789</v>
       </c>
       <c r="L63" t="s">
         <v>15</v>
@@ -3228,10 +3228,10 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>1843</v>
+        <v>791</v>
       </c>
       <c r="D64">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="E64">
         <v>48</v>
@@ -3240,19 +3240,19 @@
         <v>1809.56</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I64">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J64">
-        <v>1.8789</v>
+        <v>2.5421</v>
       </c>
       <c r="K64">
-        <v>1.8789</v>
+        <v>1.3263</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3272,10 +3272,10 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>1434</v>
+        <v>1594</v>
       </c>
       <c r="D65">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E65">
         <v>48</v>
@@ -3284,19 +3284,19 @@
         <v>1809.56</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>3.8683</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>2.2657</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3580,10 +3580,10 @@
         <v>71</v>
       </c>
       <c r="C72">
-        <v>1443</v>
+        <v>1520</v>
       </c>
       <c r="D72">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="E72">
         <v>50</v>
@@ -3800,16 +3800,16 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1024</v>
+        <v>1359</v>
       </c>
       <c r="D77">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="E77">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F77">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3844,31 +3844,31 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>1116</v>
+        <v>1442</v>
       </c>
       <c r="D78">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E78">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F78">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I78">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J78">
-        <v>1.3263</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>1.3263</v>
+        <v>0</v>
       </c>
       <c r="L78" t="s">
         <v>15</v>
@@ -3888,16 +3888,16 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>1359</v>
+        <v>1026</v>
       </c>
       <c r="D79">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="E79">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F79">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3932,31 +3932,31 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>1521</v>
+        <v>1117</v>
       </c>
       <c r="D80">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F80">
-        <v>1963.5</v>
+        <v>1661.9</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>1.5645</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>1.5645</v>
       </c>
       <c r="L80" t="s">
         <v>15</v>
@@ -3976,7 +3976,7 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>1940</v>
+        <v>1928</v>
       </c>
       <c r="D81">
         <v>1407</v>
@@ -3988,19 +3988,19 @@
         <v>2123.72</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>5.0383</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>3.6257</v>
+        <v>0</v>
       </c>
       <c r="L81" t="s">
         <v>15</v>
@@ -4020,31 +4020,31 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>701</v>
+        <v>1121</v>
       </c>
       <c r="D82">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="E82">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F82">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I82">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J82">
-        <v>2.4868</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>2.4868</v>
+        <v>0</v>
       </c>
       <c r="L82" t="s">
         <v>15</v>
@@ -4064,31 +4064,31 @@
         <v>82</v>
       </c>
       <c r="C83">
-        <v>951</v>
+        <v>701</v>
       </c>
       <c r="D83">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E83">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F83">
-        <v>1520.53</v>
+        <v>1809.56</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
       <c r="H83">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I83">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="J83">
-        <v>1.3153</v>
+        <v>2.4868</v>
       </c>
       <c r="K83">
-        <v>1.3153</v>
+        <v>2.4868</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
@@ -4108,31 +4108,31 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>1602</v>
+        <v>951</v>
       </c>
       <c r="D84">
         <v>1464</v>
       </c>
       <c r="E84">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F84">
-        <v>1963.5</v>
+        <v>1520.53</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>1.3153</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>1.3153</v>
       </c>
       <c r="L84" t="s">
         <v>15</v>
@@ -4152,16 +4152,16 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>1684</v>
+        <v>1602</v>
       </c>
       <c r="D85">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E85">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F85">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>85</v>
       </c>
       <c r="C86">
-        <v>1764</v>
+        <v>1684</v>
       </c>
       <c r="D86">
         <v>1463</v>
@@ -4240,16 +4240,16 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>1849</v>
+        <v>1764</v>
       </c>
       <c r="D87">
         <v>1463</v>
       </c>
       <c r="E87">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F87">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -4284,10 +4284,10 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>787</v>
+        <v>1849</v>
       </c>
       <c r="D88">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E88">
         <v>50</v>
@@ -4296,19 +4296,19 @@
         <v>1963.5</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I88">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J88">
-        <v>3.5141</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>3.5141</v>
+        <v>0</v>
       </c>
       <c r="L88" t="s">
         <v>15</v>
@@ -4328,31 +4328,31 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>873</v>
+        <v>787</v>
       </c>
       <c r="D89">
         <v>1464</v>
       </c>
       <c r="E89">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F89">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="I89">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="J89">
-        <v>2.3467</v>
+        <v>3.5141</v>
       </c>
       <c r="K89">
-        <v>2.3467</v>
+        <v>3.5141</v>
       </c>
       <c r="L89" t="s">
         <v>15</v>
@@ -4372,31 +4372,31 @@
         <v>89</v>
       </c>
       <c r="C90">
-        <v>1037</v>
+        <v>873</v>
       </c>
       <c r="D90">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="E90">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F90">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G90">
         <v>1</v>
       </c>
       <c r="H90">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I90">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J90">
-        <v>1.3263</v>
+        <v>2.3467</v>
       </c>
       <c r="K90">
-        <v>1.3263</v>
+        <v>2.3467</v>
       </c>
       <c r="L90" t="s">
         <v>15</v>
@@ -4416,31 +4416,31 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>1118</v>
+        <v>1037</v>
       </c>
       <c r="D91">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="E91">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F91">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>1.3263</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>1.3263</v>
       </c>
       <c r="L91" t="s">
         <v>15</v>
@@ -4507,7 +4507,7 @@
         <v>1276</v>
       </c>
       <c r="D93">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E93">
         <v>52</v>
@@ -4812,31 +4812,31 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="D100">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="E100">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F100">
-        <v>2123.72</v>
+        <v>1520.53</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I100">
         <v>16</v>
       </c>
       <c r="J100">
-        <v>0.7534</v>
+        <v>2.1045</v>
       </c>
       <c r="K100">
-        <v>0.7534</v>
+        <v>1.0523</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -5120,31 +5120,31 @@
         <v>106</v>
       </c>
       <c r="C107">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="D107">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="E107">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F107">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H107">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="I107">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J107">
-        <v>5.4621</v>
+        <v>3.3104</v>
       </c>
       <c r="K107">
-        <v>2.2602</v>
+        <v>1.8335</v>
       </c>
       <c r="L107" t="s">
         <v>15</v>
@@ -5164,10 +5164,10 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="D108">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="E108">
         <v>48</v>
@@ -5472,31 +5472,31 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D115">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="E115">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F115">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I115">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>1.3655</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>1.3655</v>
+        <v>0</v>
       </c>
       <c r="L115" t="s">
         <v>15</v>
@@ -5736,7 +5736,7 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="D121">
         <v>1570</v>
@@ -5780,10 +5780,10 @@
         <v>121</v>
       </c>
       <c r="C122">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D122">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="E122">
         <v>48</v>
@@ -5956,10 +5956,10 @@
         <v>125</v>
       </c>
       <c r="C126">
-        <v>1199</v>
+        <v>1942</v>
       </c>
       <c r="D126">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="E126">
         <v>52</v>
@@ -5971,16 +5971,16 @@
         <v>1</v>
       </c>
       <c r="H126">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="I126">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="J126">
-        <v>2.8723</v>
+        <v>0.9888</v>
       </c>
       <c r="K126">
-        <v>2.8723</v>
+        <v>0.9888</v>
       </c>
       <c r="L126" t="s">
         <v>15</v>
@@ -6000,10 +6000,10 @@
         <v>126</v>
       </c>
       <c r="C127">
-        <v>1277</v>
+        <v>1199</v>
       </c>
       <c r="D127">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="E127">
         <v>52</v>
@@ -6012,19 +6012,19 @@
         <v>2123.72</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>2.8723</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>2.8723</v>
       </c>
       <c r="L127" t="s">
         <v>15</v>
@@ -6044,7 +6044,7 @@
         <v>127</v>
       </c>
       <c r="C128">
-        <v>1360</v>
+        <v>1277</v>
       </c>
       <c r="D128">
         <v>1573</v>
@@ -6088,7 +6088,7 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>1953</v>
+        <v>1360</v>
       </c>
       <c r="D129">
         <v>1573</v>
@@ -6100,19 +6100,19 @@
         <v>2123.72</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I129">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>0.9888</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>0.9888</v>
+        <v>0</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -6176,31 +6176,31 @@
         <v>130</v>
       </c>
       <c r="C131">
-        <v>1694</v>
+        <v>1442</v>
       </c>
       <c r="D131">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="E131">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F131">
-        <v>1661.9</v>
+        <v>1963.5</v>
       </c>
       <c r="G131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="I131">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="J131">
-        <v>2.106</v>
+        <v>3.4632</v>
       </c>
       <c r="K131">
-        <v>2.106</v>
+        <v>2.6483</v>
       </c>
       <c r="L131" t="s">
         <v>15</v>
@@ -6220,16 +6220,16 @@
         <v>131</v>
       </c>
       <c r="C132">
-        <v>1776</v>
+        <v>1107</v>
       </c>
       <c r="D132">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="E132">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F132">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -6241,10 +6241,10 @@
         <v>16</v>
       </c>
       <c r="J132">
-        <v>0.8842</v>
+        <v>0.8149</v>
       </c>
       <c r="K132">
-        <v>0.8842</v>
+        <v>0.8149</v>
       </c>
       <c r="L132" t="s">
         <v>15</v>
@@ -6264,31 +6264,31 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>1861</v>
+        <v>1694</v>
       </c>
       <c r="D133">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="E133">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F133">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G133">
         <v>1</v>
       </c>
       <c r="H133">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I133">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J133">
-        <v>1.5473</v>
+        <v>2.106</v>
       </c>
       <c r="K133">
-        <v>1.5473</v>
+        <v>2.106</v>
       </c>
       <c r="L133" t="s">
         <v>15</v>
@@ -6308,31 +6308,31 @@
         <v>133</v>
       </c>
       <c r="C134">
-        <v>1944</v>
+        <v>1776</v>
       </c>
       <c r="D134">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="E134">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F134">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="I134">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J134">
-        <v>4.212</v>
+        <v>0.8842</v>
       </c>
       <c r="K134">
-        <v>2.7679</v>
+        <v>0.8842</v>
       </c>
       <c r="L134" t="s">
         <v>15</v>
@@ -6352,31 +6352,31 @@
         <v>134</v>
       </c>
       <c r="C135">
-        <v>778</v>
+        <v>1861</v>
       </c>
       <c r="D135">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="E135">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F135">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I135">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J135">
-        <v>4.5204</v>
+        <v>1.5473</v>
       </c>
       <c r="K135">
-        <v>2.4015</v>
+        <v>1.5473</v>
       </c>
       <c r="L135" t="s">
         <v>15</v>
@@ -6396,31 +6396,31 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>865</v>
+        <v>1944</v>
       </c>
       <c r="D136">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="E136">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F136">
-        <v>1809.56</v>
+        <v>1661.9</v>
       </c>
       <c r="G136">
         <v>2</v>
       </c>
       <c r="H136">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I136">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J136">
-        <v>2.3763</v>
+        <v>4.212</v>
       </c>
       <c r="K136">
-        <v>1.4921</v>
+        <v>2.7679</v>
       </c>
       <c r="L136" t="s">
         <v>15</v>
@@ -6440,7 +6440,7 @@
         <v>136</v>
       </c>
       <c r="C137">
-        <v>945</v>
+        <v>778</v>
       </c>
       <c r="D137">
         <v>1624</v>
@@ -6452,19 +6452,19 @@
         <v>2123.72</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="I137">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="J137">
-        <v>3.2019</v>
+        <v>4.5204</v>
       </c>
       <c r="K137">
-        <v>3.2019</v>
+        <v>2.4015</v>
       </c>
       <c r="L137" t="s">
         <v>15</v>
@@ -6484,31 +6484,31 @@
         <v>137</v>
       </c>
       <c r="C138">
-        <v>1029</v>
+        <v>865</v>
       </c>
       <c r="D138">
         <v>1624</v>
       </c>
       <c r="E138">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F138">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="I138">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="J138">
-        <v>3.8612</v>
+        <v>2.3763</v>
       </c>
       <c r="K138">
-        <v>3.8612</v>
+        <v>1.4921</v>
       </c>
       <c r="L138" t="s">
         <v>15</v>
@@ -6528,31 +6528,31 @@
         <v>138</v>
       </c>
       <c r="C139">
-        <v>1525</v>
+        <v>945</v>
       </c>
       <c r="D139">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="E139">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F139">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>3.2019</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>3.2019</v>
       </c>
       <c r="L139" t="s">
         <v>15</v>
@@ -6572,31 +6572,31 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>1611</v>
+        <v>1029</v>
       </c>
       <c r="D140">
         <v>1624</v>
       </c>
       <c r="E140">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F140">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G140">
         <v>1</v>
       </c>
       <c r="H140">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="I140">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="J140">
-        <v>1.0695</v>
+        <v>3.8612</v>
       </c>
       <c r="K140">
-        <v>1.0695</v>
+        <v>3.8612</v>
       </c>
       <c r="L140" t="s">
         <v>15</v>
@@ -6616,31 +6616,31 @@
         <v>140</v>
       </c>
       <c r="C141">
-        <v>1278</v>
+        <v>1525</v>
       </c>
       <c r="D141">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="E141">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F141">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I141">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J141">
-        <v>3.6473</v>
+        <v>0</v>
       </c>
       <c r="K141">
-        <v>2.4315</v>
+        <v>0</v>
       </c>
       <c r="L141" t="s">
         <v>15</v>
@@ -6660,31 +6660,31 @@
         <v>141</v>
       </c>
       <c r="C142">
-        <v>1361</v>
+        <v>1611</v>
       </c>
       <c r="D142">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="E142">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F142">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G142">
         <v>1</v>
       </c>
       <c r="H142">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I142">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J142">
-        <v>1.1772</v>
+        <v>1.0695</v>
       </c>
       <c r="K142">
-        <v>1.1772</v>
+        <v>1.0695</v>
       </c>
       <c r="L142" t="s">
         <v>15</v>
@@ -6704,31 +6704,31 @@
         <v>142</v>
       </c>
       <c r="C143">
-        <v>1197</v>
+        <v>1278</v>
       </c>
       <c r="D143">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="E143">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F143">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H143">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="I143">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="J143">
-        <v>1.1714</v>
+        <v>3.6473</v>
       </c>
       <c r="K143">
-        <v>1.1714</v>
+        <v>2.4315</v>
       </c>
       <c r="L143" t="s">
         <v>15</v>
@@ -6748,31 +6748,31 @@
         <v>143</v>
       </c>
       <c r="C144">
-        <v>1108</v>
+        <v>1361</v>
       </c>
       <c r="D144">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="E144">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F144">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G144">
         <v>1</v>
       </c>
       <c r="H144">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I144">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J144">
-        <v>0.8149</v>
+        <v>1.1772</v>
       </c>
       <c r="K144">
-        <v>0.8149</v>
+        <v>1.1772</v>
       </c>
       <c r="L144" t="s">
         <v>15</v>
@@ -6792,10 +6792,10 @@
         <v>144</v>
       </c>
       <c r="C145">
-        <v>1442</v>
+        <v>1197</v>
       </c>
       <c r="D145">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="E145">
         <v>50</v>
@@ -6804,19 +6804,19 @@
         <v>1963.5</v>
       </c>
       <c r="G145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="I145">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J145">
-        <v>3.4632</v>
+        <v>1.1714</v>
       </c>
       <c r="K145">
-        <v>2.6483</v>
+        <v>1.1714</v>
       </c>
       <c r="L145" t="s">
         <v>15</v>
@@ -6880,7 +6880,7 @@
         <v>146</v>
       </c>
       <c r="C147">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="D147">
         <v>1672</v>
@@ -7059,13 +7059,13 @@
         <v>1698</v>
       </c>
       <c r="D151">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E151">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F151">
-        <v>1661.9</v>
+        <v>1809.56</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -7077,10 +7077,10 @@
         <v>19</v>
       </c>
       <c r="J151">
-        <v>1.1433</v>
+        <v>1.05</v>
       </c>
       <c r="K151">
-        <v>1.1433</v>
+        <v>1.05</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -7144,16 +7144,16 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>1853</v>
+        <v>1865</v>
       </c>
       <c r="D153">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="E153">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F153">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -7367,13 +7367,13 @@
         <v>1278</v>
       </c>
       <c r="D158">
-        <v>1669</v>
+        <v>1680</v>
       </c>
       <c r="E158">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F158">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -7584,31 +7584,31 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="D163">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="E163">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F163">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G163">
         <v>2</v>
       </c>
       <c r="H163">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I163">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J163">
-        <v>4.1437</v>
+        <v>4.8383</v>
       </c>
       <c r="K163">
-        <v>3.3432</v>
+        <v>3.9216</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7672,10 +7672,10 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="D165">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="E165">
         <v>52</v>
@@ -7687,16 +7687,16 @@
         <v>1</v>
       </c>
       <c r="H165">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I165">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J165">
-        <v>0.7534</v>
+        <v>1.3655</v>
       </c>
       <c r="K165">
-        <v>0.7534</v>
+        <v>1.3655</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7760,31 +7760,31 @@
         <v>166</v>
       </c>
       <c r="C167">
-        <v>1786</v>
+        <v>1191</v>
       </c>
       <c r="D167">
-        <v>1734</v>
+        <v>1741</v>
       </c>
       <c r="E167">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F167">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H167">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="I167">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J167">
-        <v>2.6483</v>
+        <v>3.4374</v>
       </c>
       <c r="K167">
-        <v>1.3242</v>
+        <v>1.8835</v>
       </c>
       <c r="L167" t="s">
         <v>15</v>
@@ -7804,10 +7804,10 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>1874</v>
+        <v>1786</v>
       </c>
       <c r="D168">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="E168">
         <v>50</v>
@@ -7816,19 +7816,19 @@
         <v>1963.5</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H168">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="I168">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="J168">
-        <v>4.1762</v>
+        <v>2.6483</v>
       </c>
       <c r="K168">
-        <v>4.1762</v>
+        <v>1.3242</v>
       </c>
       <c r="L168" t="s">
         <v>15</v>
@@ -7848,31 +7848,31 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>851</v>
+        <v>1875</v>
       </c>
       <c r="D169">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="E169">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F169">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>4.1762</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>4.1762</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7892,10 +7892,10 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>942</v>
+        <v>851</v>
       </c>
       <c r="D170">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="E170">
         <v>52</v>
@@ -7904,19 +7904,19 @@
         <v>2123.72</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I170">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J170">
-        <v>0.7534</v>
+        <v>0</v>
       </c>
       <c r="K170">
-        <v>0.7534</v>
+        <v>0</v>
       </c>
       <c r="L170" t="s">
         <v>15</v>
@@ -7936,10 +7936,10 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>1280</v>
+        <v>942</v>
       </c>
       <c r="D171">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E171">
         <v>52</v>
@@ -7948,19 +7948,19 @@
         <v>2123.72</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>0.7534</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>0.7534</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -7980,10 +7980,10 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>1363</v>
+        <v>1280</v>
       </c>
       <c r="D172">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E172">
         <v>52</v>
@@ -7992,19 +7992,19 @@
         <v>2123.72</v>
       </c>
       <c r="G172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="I172">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J172">
-        <v>3.4374</v>
+        <v>0</v>
       </c>
       <c r="K172">
-        <v>1.5068</v>
+        <v>0</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8024,10 +8024,10 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>1443</v>
+        <v>1363</v>
       </c>
       <c r="D173">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="E173">
         <v>52</v>
@@ -8036,19 +8036,19 @@
         <v>2123.72</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H173">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I173">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="J173">
-        <v>2.7311</v>
+        <v>3.4374</v>
       </c>
       <c r="K173">
-        <v>2.7311</v>
+        <v>1.5068</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -8068,31 +8068,31 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>1532</v>
+        <v>1443</v>
       </c>
       <c r="D174">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="E174">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F174">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174">
         <v>58</v>
       </c>
       <c r="I174">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="J174">
-        <v>3.2052</v>
+        <v>2.7311</v>
       </c>
       <c r="K174">
-        <v>1.7131</v>
+        <v>2.7311</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8112,31 +8112,31 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1618</v>
+        <v>1532</v>
       </c>
       <c r="D175">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="E175">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F175">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H175">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I175">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J175">
-        <v>2.1189</v>
+        <v>3.2052</v>
       </c>
       <c r="K175">
-        <v>2.1189</v>
+        <v>1.7131</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8156,10 +8156,10 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>1692</v>
+        <v>1618</v>
       </c>
       <c r="D176">
-        <v>1738</v>
+        <v>1731</v>
       </c>
       <c r="E176">
         <v>52</v>
@@ -8168,19 +8168,19 @@
         <v>2123.72</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I176">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>2.1189</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>2.1189</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8200,10 +8200,10 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>1190</v>
+        <v>1692</v>
       </c>
       <c r="D177">
-        <v>1742</v>
+        <v>1738</v>
       </c>
       <c r="E177">
         <v>52</v>
@@ -8212,19 +8212,19 @@
         <v>2123.72</v>
       </c>
       <c r="G177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J177">
-        <v>2.6369</v>
+        <v>0</v>
       </c>
       <c r="K177">
-        <v>1.8835</v>
+        <v>0</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -8288,31 +8288,31 @@
         <v>178</v>
       </c>
       <c r="C179">
-        <v>1875</v>
+        <v>1620</v>
       </c>
       <c r="D179">
         <v>1790</v>
       </c>
       <c r="E179">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F179">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H179">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I179">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J179">
-        <v>1.3242</v>
+        <v>1.7893</v>
       </c>
       <c r="K179">
-        <v>1.3242</v>
+        <v>1.0359</v>
       </c>
       <c r="L179" t="s">
         <v>15</v>
@@ -8332,7 +8332,7 @@
         <v>179</v>
       </c>
       <c r="C180">
-        <v>1960</v>
+        <v>1875</v>
       </c>
       <c r="D180">
         <v>1790</v>
@@ -8344,19 +8344,19 @@
         <v>1963.5</v>
       </c>
       <c r="G180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H180">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="I180">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J180">
-        <v>4.1253</v>
+        <v>1.3242</v>
       </c>
       <c r="K180">
-        <v>2.19</v>
+        <v>1.3242</v>
       </c>
       <c r="L180" t="s">
         <v>15</v>
@@ -8376,31 +8376,31 @@
         <v>180</v>
       </c>
       <c r="C181">
-        <v>762</v>
+        <v>1960</v>
       </c>
       <c r="D181">
         <v>1790</v>
       </c>
       <c r="E181">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F181">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="I181">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J181">
-        <v>1.9306</v>
+        <v>4.1253</v>
       </c>
       <c r="K181">
-        <v>1.9306</v>
+        <v>2.19</v>
       </c>
       <c r="L181" t="s">
         <v>15</v>
@@ -8420,31 +8420,31 @@
         <v>181</v>
       </c>
       <c r="C182">
-        <v>850</v>
+        <v>762</v>
       </c>
       <c r="D182">
         <v>1790</v>
       </c>
       <c r="E182">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F182">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G182">
         <v>1</v>
       </c>
       <c r="H182">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="I182">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J182">
-        <v>3.7179</v>
+        <v>1.9306</v>
       </c>
       <c r="K182">
-        <v>3.7179</v>
+        <v>1.9306</v>
       </c>
       <c r="L182" t="s">
         <v>15</v>
@@ -8464,31 +8464,31 @@
         <v>182</v>
       </c>
       <c r="C183">
-        <v>939</v>
+        <v>850</v>
       </c>
       <c r="D183">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="E183">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F183">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G183">
         <v>1</v>
       </c>
       <c r="H183">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="I183">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="J183">
-        <v>1.8789</v>
+        <v>3.7179</v>
       </c>
       <c r="K183">
-        <v>1.8789</v>
+        <v>3.7179</v>
       </c>
       <c r="L183" t="s">
         <v>15</v>
@@ -8508,31 +8508,31 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>1024</v>
+        <v>939</v>
       </c>
       <c r="D184">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E184">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F184">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>1.8789</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>1.8789</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8552,10 +8552,10 @@
         <v>184</v>
       </c>
       <c r="C185">
-        <v>1108</v>
+        <v>1024</v>
       </c>
       <c r="D185">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="E185">
         <v>52</v>
@@ -8564,19 +8564,19 @@
         <v>2123.72</v>
       </c>
       <c r="G185">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I185">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J185">
-        <v>4.0024</v>
+        <v>0</v>
       </c>
       <c r="K185">
-        <v>2.9665</v>
+        <v>0</v>
       </c>
       <c r="L185" t="s">
         <v>15</v>
@@ -8596,10 +8596,10 @@
         <v>185</v>
       </c>
       <c r="C186">
-        <v>1194</v>
+        <v>1108</v>
       </c>
       <c r="D186">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="E186">
         <v>52</v>
@@ -8608,19 +8608,19 @@
         <v>2123.72</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>4.0024</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>2.9665</v>
       </c>
       <c r="L186" t="s">
         <v>15</v>
@@ -8640,10 +8640,10 @@
         <v>186</v>
       </c>
       <c r="C187">
-        <v>1279</v>
+        <v>1194</v>
       </c>
       <c r="D187">
-        <v>1802</v>
+        <v>1791</v>
       </c>
       <c r="E187">
         <v>52</v>
@@ -8684,31 +8684,31 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>1368</v>
+        <v>1280</v>
       </c>
       <c r="D188">
         <v>1791</v>
       </c>
       <c r="E188">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F188">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I188">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J188">
-        <v>1.1714</v>
+        <v>0</v>
       </c>
       <c r="K188">
-        <v>1.1714</v>
+        <v>0</v>
       </c>
       <c r="L188" t="s">
         <v>15</v>
@@ -8728,10 +8728,10 @@
         <v>188</v>
       </c>
       <c r="C189">
-        <v>1538</v>
+        <v>1368</v>
       </c>
       <c r="D189">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E189">
         <v>50</v>
@@ -8743,16 +8743,16 @@
         <v>1</v>
       </c>
       <c r="H189">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I189">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="J189">
-        <v>2.19</v>
+        <v>1.1714</v>
       </c>
       <c r="K189">
-        <v>2.19</v>
+        <v>1.1714</v>
       </c>
       <c r="L189" t="s">
         <v>15</v>
@@ -8772,10 +8772,10 @@
         <v>189</v>
       </c>
       <c r="C190">
-        <v>1705</v>
+        <v>1538</v>
       </c>
       <c r="D190">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E190">
         <v>50</v>
@@ -8784,19 +8784,19 @@
         <v>1963.5</v>
       </c>
       <c r="G190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H190">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="I190">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J190">
-        <v>3.1576</v>
+        <v>2.19</v>
       </c>
       <c r="K190">
-        <v>1.8335</v>
+        <v>2.19</v>
       </c>
       <c r="L190" t="s">
         <v>15</v>
@@ -8816,7 +8816,7 @@
         <v>190</v>
       </c>
       <c r="C191">
-        <v>1790</v>
+        <v>1705</v>
       </c>
       <c r="D191">
         <v>1791</v>
@@ -8831,16 +8831,16 @@
         <v>2</v>
       </c>
       <c r="H191">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I191">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="J191">
-        <v>3.4123</v>
+        <v>3.1576</v>
       </c>
       <c r="K191">
-        <v>2.4955</v>
+        <v>1.8335</v>
       </c>
       <c r="L191" t="s">
         <v>15</v>
@@ -8860,31 +8860,31 @@
         <v>191</v>
       </c>
       <c r="C192">
-        <v>1449</v>
+        <v>1790</v>
       </c>
       <c r="D192">
         <v>1791</v>
       </c>
       <c r="E192">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F192">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I192">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J192">
-        <v>3.371</v>
+        <v>3.4123</v>
       </c>
       <c r="K192">
-        <v>3.371</v>
+        <v>2.4955</v>
       </c>
       <c r="L192" t="s">
         <v>15</v>
@@ -8904,31 +8904,31 @@
         <v>192</v>
       </c>
       <c r="C193">
-        <v>1630</v>
+        <v>1449</v>
       </c>
       <c r="D193">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E193">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F193">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H193">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="I193">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J193">
-        <v>1.7893</v>
+        <v>3.371</v>
       </c>
       <c r="K193">
-        <v>1.0359</v>
+        <v>3.371</v>
       </c>
       <c r="L193" t="s">
         <v>15</v>
@@ -9036,7 +9036,7 @@
         <v>195</v>
       </c>
       <c r="C196">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D196">
         <v>1857</v>
@@ -9080,10 +9080,10 @@
         <v>196</v>
       </c>
       <c r="C197">
-        <v>1019</v>
+        <v>1708</v>
       </c>
       <c r="D197">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E197">
         <v>52</v>
@@ -9095,16 +9095,16 @@
         <v>2</v>
       </c>
       <c r="H197">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I197">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J197">
-        <v>3.4845</v>
+        <v>3.6257</v>
       </c>
       <c r="K197">
-        <v>1.9777</v>
+        <v>1.8835</v>
       </c>
       <c r="L197" t="s">
         <v>15</v>
@@ -9124,31 +9124,31 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>1708</v>
+        <v>1796</v>
       </c>
       <c r="D198">
         <v>1848</v>
       </c>
       <c r="E198">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F198">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H198">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I198">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J198">
-        <v>3.6257</v>
+        <v>1.3263</v>
       </c>
       <c r="K198">
-        <v>1.8835</v>
+        <v>1.3263</v>
       </c>
       <c r="L198" t="s">
         <v>15</v>
@@ -9168,31 +9168,31 @@
         <v>198</v>
       </c>
       <c r="C199">
-        <v>1796</v>
+        <v>1880</v>
       </c>
       <c r="D199">
         <v>1848</v>
       </c>
       <c r="E199">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F199">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G199">
         <v>1</v>
       </c>
       <c r="H199">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="I199">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="J199">
-        <v>1.3263</v>
+        <v>3.7688</v>
       </c>
       <c r="K199">
-        <v>1.3263</v>
+        <v>3.7688</v>
       </c>
       <c r="L199" t="s">
         <v>15</v>
@@ -9212,10 +9212,10 @@
         <v>199</v>
       </c>
       <c r="C200">
-        <v>1880</v>
+        <v>853</v>
       </c>
       <c r="D200">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="E200">
         <v>50</v>
@@ -9224,19 +9224,19 @@
         <v>1963.5</v>
       </c>
       <c r="G200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H200">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I200">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="J200">
-        <v>3.7688</v>
+        <v>3.5141</v>
       </c>
       <c r="K200">
-        <v>3.7688</v>
+        <v>2.2409</v>
       </c>
       <c r="L200" t="s">
         <v>15</v>
@@ -9256,31 +9256,31 @@
         <v>200</v>
       </c>
       <c r="C201">
-        <v>853</v>
+        <v>937</v>
       </c>
       <c r="D201">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="E201">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F201">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G201">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H201">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I201">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J201">
-        <v>3.5141</v>
+        <v>0</v>
       </c>
       <c r="K201">
-        <v>2.2409</v>
+        <v>0</v>
       </c>
       <c r="L201" t="s">
         <v>15</v>
@@ -9300,7 +9300,7 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>937</v>
+        <v>1108</v>
       </c>
       <c r="D202">
         <v>1849</v>
@@ -9312,19 +9312,19 @@
         <v>2123.72</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I202">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J202">
-        <v>0</v>
+        <v>3.249</v>
       </c>
       <c r="K202">
-        <v>0</v>
+        <v>2.3073</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -9344,31 +9344,31 @@
         <v>202</v>
       </c>
       <c r="C203">
-        <v>1108</v>
+        <v>1195</v>
       </c>
       <c r="D203">
         <v>1849</v>
       </c>
       <c r="E203">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F203">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G203">
         <v>2</v>
       </c>
       <c r="H203">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I203">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J203">
-        <v>3.249</v>
+        <v>3.4263</v>
       </c>
       <c r="K203">
-        <v>2.3073</v>
+        <v>2.1</v>
       </c>
       <c r="L203" t="s">
         <v>15</v>
@@ -9388,31 +9388,31 @@
         <v>203</v>
       </c>
       <c r="C204">
-        <v>1195</v>
+        <v>1280</v>
       </c>
       <c r="D204">
         <v>1849</v>
       </c>
       <c r="E204">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F204">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H204">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="I204">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J204">
-        <v>3.4263</v>
+        <v>4.3791</v>
       </c>
       <c r="K204">
-        <v>2.1</v>
+        <v>4.3791</v>
       </c>
       <c r="L204" t="s">
         <v>15</v>
@@ -9432,10 +9432,10 @@
         <v>204</v>
       </c>
       <c r="C205">
-        <v>1279</v>
+        <v>1366</v>
       </c>
       <c r="D205">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="E205">
         <v>52</v>
@@ -9447,16 +9447,16 @@
         <v>1</v>
       </c>
       <c r="H205">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I205">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J205">
-        <v>4.3791</v>
+        <v>3.5786</v>
       </c>
       <c r="K205">
-        <v>4.3791</v>
+        <v>3.5786</v>
       </c>
       <c r="L205" t="s">
         <v>15</v>
@@ -9476,31 +9476,31 @@
         <v>205</v>
       </c>
       <c r="C206">
-        <v>1366</v>
+        <v>1451</v>
       </c>
       <c r="D206">
         <v>1849</v>
       </c>
       <c r="E206">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F206">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G206">
         <v>1</v>
       </c>
       <c r="H206">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="I206">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="J206">
-        <v>3.5786</v>
+        <v>2.321</v>
       </c>
       <c r="K206">
-        <v>3.5786</v>
+        <v>2.321</v>
       </c>
       <c r="L206" t="s">
         <v>15</v>
@@ -9520,31 +9520,31 @@
         <v>206</v>
       </c>
       <c r="C207">
-        <v>1451</v>
+        <v>1533</v>
       </c>
       <c r="D207">
         <v>1849</v>
       </c>
       <c r="E207">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F207">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G207">
         <v>1</v>
       </c>
       <c r="H207">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I207">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="J207">
-        <v>2.321</v>
+        <v>3.0558</v>
       </c>
       <c r="K207">
-        <v>2.321</v>
+        <v>3.0558</v>
       </c>
       <c r="L207" t="s">
         <v>15</v>
@@ -9564,31 +9564,31 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>1533</v>
+        <v>1019</v>
       </c>
       <c r="D208">
         <v>1849</v>
       </c>
       <c r="E208">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F208">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H208">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="I208">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="J208">
-        <v>3.0558</v>
+        <v>3.4845</v>
       </c>
       <c r="K208">
-        <v>3.0558</v>
+        <v>1.9777</v>
       </c>
       <c r="L208" t="s">
         <v>15</v>
@@ -9652,10 +9652,10 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>936</v>
+        <v>1196</v>
       </c>
       <c r="D210">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E210">
         <v>52</v>
@@ -9664,19 +9664,19 @@
         <v>2123.72</v>
       </c>
       <c r="G210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H210">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I210">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J210">
-        <v>2.8252</v>
+        <v>3.4374</v>
       </c>
       <c r="K210">
-        <v>2.8252</v>
+        <v>2.684</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9696,31 +9696,31 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>1196</v>
+        <v>677</v>
       </c>
       <c r="D211">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="E211">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F211">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G211">
         <v>2</v>
       </c>
       <c r="H211">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I211">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J211">
-        <v>3.4374</v>
+        <v>3.5651</v>
       </c>
       <c r="K211">
-        <v>2.684</v>
+        <v>2.7502</v>
       </c>
       <c r="L211" t="s">
         <v>15</v>
@@ -9740,31 +9740,31 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>677</v>
+        <v>760</v>
       </c>
       <c r="D212">
-        <v>1907</v>
+        <v>1916</v>
       </c>
       <c r="E212">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F212">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H212">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="I212">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="J212">
-        <v>3.5651</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K212">
-        <v>2.7502</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9784,10 +9784,10 @@
         <v>212</v>
       </c>
       <c r="C213">
-        <v>758</v>
+        <v>845</v>
       </c>
       <c r="D213">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="E213">
         <v>52</v>
@@ -9796,19 +9796,19 @@
         <v>2123.72</v>
       </c>
       <c r="G213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I213">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J213">
-        <v>1.3655</v>
+        <v>0</v>
       </c>
       <c r="K213">
-        <v>1.3655</v>
+        <v>0</v>
       </c>
       <c r="L213" t="s">
         <v>15</v>
@@ -9828,10 +9828,10 @@
         <v>213</v>
       </c>
       <c r="C214">
-        <v>845</v>
+        <v>1281</v>
       </c>
       <c r="D214">
-        <v>1918</v>
+        <v>1904</v>
       </c>
       <c r="E214">
         <v>52</v>
@@ -9840,19 +9840,19 @@
         <v>2123.72</v>
       </c>
       <c r="G214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I214">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J214">
-        <v>0</v>
+        <v>1.5539</v>
       </c>
       <c r="K214">
-        <v>0</v>
+        <v>1.5539</v>
       </c>
       <c r="L214" t="s">
         <v>15</v>
@@ -9872,10 +9872,10 @@
         <v>214</v>
       </c>
       <c r="C215">
-        <v>1281</v>
+        <v>1541</v>
       </c>
       <c r="D215">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E215">
         <v>52</v>
@@ -9884,19 +9884,19 @@
         <v>2123.72</v>
       </c>
       <c r="G215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I215">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J215">
-        <v>1.5539</v>
+        <v>0</v>
       </c>
       <c r="K215">
-        <v>1.5539</v>
+        <v>0</v>
       </c>
       <c r="L215" t="s">
         <v>15</v>
@@ -9916,31 +9916,31 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>1541</v>
+        <v>1885</v>
       </c>
       <c r="D216">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="E216">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F216">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J216">
-        <v>0</v>
+        <v>7.3339</v>
       </c>
       <c r="K216">
-        <v>0</v>
+        <v>4.4309</v>
       </c>
       <c r="L216" t="s">
         <v>15</v>
@@ -9960,7 +9960,7 @@
         <v>216</v>
       </c>
       <c r="C217">
-        <v>1885</v>
+        <v>1971</v>
       </c>
       <c r="D217">
         <v>1906</v>
@@ -9972,19 +9972,19 @@
         <v>1963.5</v>
       </c>
       <c r="G217">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="I217">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="J217">
-        <v>7.3339</v>
+        <v>0</v>
       </c>
       <c r="K217">
-        <v>4.4309</v>
+        <v>0</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -10004,10 +10004,10 @@
         <v>217</v>
       </c>
       <c r="C218">
-        <v>1971</v>
+        <v>1023</v>
       </c>
       <c r="D218">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="E218">
         <v>50</v>
@@ -10016,19 +10016,19 @@
         <v>1963.5</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J218">
-        <v>0</v>
+        <v>0.9677</v>
       </c>
       <c r="K218">
-        <v>0</v>
+        <v>0.9677</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -10048,31 +10048,31 @@
         <v>218</v>
       </c>
       <c r="C219">
-        <v>1023</v>
+        <v>1368</v>
       </c>
       <c r="D219">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="E219">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F219">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G219">
         <v>1</v>
       </c>
       <c r="H219">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I219">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J219">
-        <v>0.9677</v>
+        <v>0.9888</v>
       </c>
       <c r="K219">
-        <v>0.9677</v>
+        <v>0.9888</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -10092,7 +10092,7 @@
         <v>219</v>
       </c>
       <c r="C220">
-        <v>1368</v>
+        <v>1453</v>
       </c>
       <c r="D220">
         <v>1904</v>
@@ -10104,19 +10104,19 @@
         <v>2123.72</v>
       </c>
       <c r="G220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H220">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="I220">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="J220">
-        <v>0.9888</v>
+        <v>6.2626</v>
       </c>
       <c r="K220">
-        <v>0.9888</v>
+        <v>5.5092</v>
       </c>
       <c r="L220" t="s">
         <v>15</v>
@@ -10136,10 +10136,10 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>1453</v>
+        <v>1626</v>
       </c>
       <c r="D221">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="E221">
         <v>52</v>
@@ -10148,19 +10148,19 @@
         <v>2123.72</v>
       </c>
       <c r="G221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H221">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="I221">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="J221">
-        <v>6.2626</v>
+        <v>3.9082</v>
       </c>
       <c r="K221">
-        <v>5.5092</v>
+        <v>3.9082</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -10180,31 +10180,31 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>1626</v>
+        <v>1714</v>
       </c>
       <c r="D222">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="E222">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F222">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G222">
         <v>1</v>
       </c>
       <c r="H222">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="I222">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="J222">
-        <v>3.9082</v>
+        <v>2.6993</v>
       </c>
       <c r="K222">
-        <v>3.9082</v>
+        <v>2.6993</v>
       </c>
       <c r="L222" t="s">
         <v>15</v>
@@ -10224,31 +10224,31 @@
         <v>222</v>
       </c>
       <c r="C223">
-        <v>1714</v>
+        <v>1799</v>
       </c>
       <c r="D223">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="E223">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F223">
-        <v>1963.5</v>
+        <v>1809.56</v>
       </c>
       <c r="G223">
         <v>1</v>
       </c>
       <c r="H223">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="I223">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="J223">
-        <v>2.6993</v>
+        <v>4.9736</v>
       </c>
       <c r="K223">
-        <v>2.6993</v>
+        <v>4.9736</v>
       </c>
       <c r="L223" t="s">
         <v>15</v>
@@ -10268,31 +10268,31 @@
         <v>223</v>
       </c>
       <c r="C224">
-        <v>1799</v>
+        <v>920</v>
       </c>
       <c r="D224">
-        <v>1907</v>
+        <v>1929</v>
       </c>
       <c r="E224">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F224">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H224">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I224">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J224">
-        <v>4.9736</v>
+        <v>0</v>
       </c>
       <c r="K224">
-        <v>4.9736</v>
+        <v>0</v>
       </c>
       <c r="L224" t="s">
         <v>15</v>
@@ -10312,10 +10312,10 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D225">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="E225">
         <v>52</v>
@@ -10356,16 +10356,16 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>939</v>
+        <v>673</v>
       </c>
       <c r="D226">
-        <v>1978</v>
+        <v>1965</v>
       </c>
       <c r="E226">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F226">
-        <v>1134.11</v>
+        <v>1809.56</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -10400,10 +10400,10 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>1701</v>
+        <v>758</v>
       </c>
       <c r="D227">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="E227">
         <v>52</v>
@@ -10444,31 +10444,31 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>1280</v>
+        <v>1890</v>
       </c>
       <c r="D228">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="E228">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F228">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H228">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="I228">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="J228">
-        <v>3.7199</v>
+        <v>5.6532</v>
       </c>
       <c r="K228">
-        <v>2.4485</v>
+        <v>5.6532</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -10488,16 +10488,16 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>673</v>
+        <v>1973</v>
       </c>
       <c r="D229">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="E229">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F229">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -10532,10 +10532,10 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>758</v>
+        <v>842</v>
       </c>
       <c r="D230">
-        <v>1953</v>
+        <v>1962</v>
       </c>
       <c r="E230">
         <v>52</v>
@@ -10544,19 +10544,19 @@
         <v>2123.72</v>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I230">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J230">
-        <v>0</v>
+        <v>3.1548</v>
       </c>
       <c r="K230">
-        <v>0</v>
+        <v>2.166</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10576,31 +10576,31 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>1890</v>
+        <v>1020</v>
       </c>
       <c r="D231">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="E231">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F231">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G231">
         <v>1</v>
       </c>
       <c r="H231">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="I231">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="J231">
-        <v>5.6532</v>
+        <v>1.083</v>
       </c>
       <c r="K231">
-        <v>5.6532</v>
+        <v>1.083</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10620,31 +10620,31 @@
         <v>231</v>
       </c>
       <c r="C232">
-        <v>1973</v>
+        <v>1368</v>
       </c>
       <c r="D232">
         <v>1966</v>
       </c>
       <c r="E232">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F232">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="I232">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J232">
-        <v>0</v>
+        <v>4.3791</v>
       </c>
       <c r="K232">
-        <v>0</v>
+        <v>4.3791</v>
       </c>
       <c r="L232" t="s">
         <v>15</v>
@@ -10664,10 +10664,10 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>842</v>
+        <v>1455</v>
       </c>
       <c r="D233">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="E233">
         <v>52</v>
@@ -10676,19 +10676,19 @@
         <v>2123.72</v>
       </c>
       <c r="G233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H233">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="I233">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J233">
-        <v>3.1548</v>
+        <v>4.9442</v>
       </c>
       <c r="K233">
-        <v>2.166</v>
+        <v>4.9442</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10708,31 +10708,31 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>1020</v>
+        <v>1544</v>
       </c>
       <c r="D234">
         <v>1966</v>
       </c>
       <c r="E234">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F234">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G234">
         <v>1</v>
       </c>
       <c r="H234">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="I234">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="J234">
-        <v>1.083</v>
+        <v>6.4681</v>
       </c>
       <c r="K234">
-        <v>1.083</v>
+        <v>6.4681</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10752,7 +10752,7 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>1368</v>
+        <v>1629</v>
       </c>
       <c r="D235">
         <v>1966</v>
@@ -10764,19 +10764,19 @@
         <v>2123.72</v>
       </c>
       <c r="G235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H235">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I235">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J235">
-        <v>4.3791</v>
+        <v>3.767</v>
       </c>
       <c r="K235">
-        <v>4.3791</v>
+        <v>1.9306</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10796,7 +10796,7 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>1455</v>
+        <v>1715</v>
       </c>
       <c r="D236">
         <v>1966</v>
@@ -10808,19 +10808,19 @@
         <v>2123.72</v>
       </c>
       <c r="G236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="I236">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="J236">
-        <v>4.9442</v>
+        <v>0</v>
       </c>
       <c r="K236">
-        <v>4.9442</v>
+        <v>0</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10840,31 +10840,31 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1544</v>
+        <v>1803</v>
       </c>
       <c r="D237">
         <v>1966</v>
       </c>
       <c r="E237">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F237">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G237">
         <v>1</v>
       </c>
       <c r="H237">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="I237">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="J237">
-        <v>6.4681</v>
+        <v>7.0631</v>
       </c>
       <c r="K237">
-        <v>6.4681</v>
+        <v>7.0631</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10884,10 +10884,10 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1629</v>
+        <v>1115</v>
       </c>
       <c r="D238">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="E238">
         <v>52</v>
@@ -10899,16 +10899,16 @@
         <v>2</v>
       </c>
       <c r="H238">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="I238">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J238">
-        <v>3.767</v>
+        <v>2.9665</v>
       </c>
       <c r="K238">
-        <v>1.9306</v>
+        <v>1.7893</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10928,31 +10928,31 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>1803</v>
+        <v>1195</v>
       </c>
       <c r="D239">
         <v>1966</v>
       </c>
       <c r="E239">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F239">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G239">
         <v>1</v>
       </c>
       <c r="H239">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="I239">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="J239">
-        <v>7.0631</v>
+        <v>4.3104</v>
       </c>
       <c r="K239">
-        <v>7.0631</v>
+        <v>4.3104</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -10972,31 +10972,31 @@
         <v>239</v>
       </c>
       <c r="C240">
-        <v>1195</v>
+        <v>1280</v>
       </c>
       <c r="D240">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="E240">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F240">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G240">
         <v>1</v>
       </c>
       <c r="H240">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I240">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="J240">
-        <v>4.3104</v>
+        <v>2.9665</v>
       </c>
       <c r="K240">
-        <v>4.3104</v>
+        <v>2.9665</v>
       </c>
       <c r="L240" t="s">
         <v>15</v>
@@ -11016,16 +11016,16 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="D241">
-        <v>2017</v>
+        <v>1983</v>
       </c>
       <c r="E241">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F241">
-        <v>2123.72</v>
+        <v>1385.44</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -11060,10 +11060,10 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>1542</v>
+        <v>942</v>
       </c>
       <c r="D242">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="E242">
         <v>52</v>
@@ -11104,31 +11104,31 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1370</v>
+        <v>1724</v>
       </c>
       <c r="D243">
-        <v>2019</v>
+        <v>2030</v>
       </c>
       <c r="E243">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F243">
-        <v>1661.9</v>
+        <v>1520.53</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I243">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J243">
-        <v>0</v>
+        <v>1.7099</v>
       </c>
       <c r="K243">
-        <v>0</v>
+        <v>1.7099</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11148,31 +11148,31 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>759</v>
+        <v>1984</v>
       </c>
       <c r="D244">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E244">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F244">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I244">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J244">
-        <v>0</v>
+        <v>1.8835</v>
       </c>
       <c r="K244">
-        <v>0</v>
+        <v>1.8835</v>
       </c>
       <c r="L244" t="s">
         <v>15</v>
@@ -11192,10 +11192,10 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>1724</v>
+        <v>1814</v>
       </c>
       <c r="D245">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="E245">
         <v>52</v>
@@ -11204,19 +11204,19 @@
         <v>2123.72</v>
       </c>
       <c r="G245">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I245">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J245">
-        <v>3.5315</v>
+        <v>0</v>
       </c>
       <c r="K245">
-        <v>2.3073</v>
+        <v>0</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -11236,10 +11236,10 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>1812</v>
+        <v>1547</v>
       </c>
       <c r="D246">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E246">
         <v>52</v>
@@ -11280,10 +11280,10 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>1984</v>
+        <v>1106</v>
       </c>
       <c r="D247">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="E247">
         <v>52</v>
@@ -11295,16 +11295,16 @@
         <v>1</v>
       </c>
       <c r="H247">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I247">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J247">
-        <v>1.8835</v>
+        <v>2.8252</v>
       </c>
       <c r="K247">
-        <v>1.8835</v>
+        <v>2.8252</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11324,10 +11324,10 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1106</v>
+        <v>1372</v>
       </c>
       <c r="D248">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E248">
         <v>52</v>
@@ -11336,19 +11336,19 @@
         <v>2123.72</v>
       </c>
       <c r="G248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I248">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J248">
-        <v>2.8252</v>
+        <v>0</v>
       </c>
       <c r="K248">
-        <v>2.8252</v>
+        <v>0</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11368,10 +11368,10 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>1899</v>
+        <v>1461</v>
       </c>
       <c r="D249">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="E249">
         <v>52</v>
@@ -11380,19 +11380,19 @@
         <v>2123.72</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I249">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1.1301</v>
       </c>
       <c r="K249">
-        <v>0</v>
+        <v>1.1301</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11412,31 +11412,31 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>667</v>
+        <v>1638</v>
       </c>
       <c r="D250">
         <v>2026</v>
       </c>
       <c r="E250">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F250">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I250">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J250">
-        <v>0</v>
+        <v>2.7311</v>
       </c>
       <c r="K250">
-        <v>0</v>
+        <v>2.7311</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11456,10 +11456,10 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>1018</v>
+        <v>1899</v>
       </c>
       <c r="D251">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="E251">
         <v>52</v>
@@ -11500,16 +11500,16 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>1596</v>
+        <v>667</v>
       </c>
       <c r="D252">
-        <v>2032</v>
+        <v>2026</v>
       </c>
       <c r="E252">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F252">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G252">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>1288</v>
+        <v>1018</v>
       </c>
       <c r="D253">
-        <v>2034</v>
+        <v>2027</v>
       </c>
       <c r="E253">
         <v>52</v>
@@ -11588,10 +11588,10 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>1184</v>
+        <v>760</v>
       </c>
       <c r="D254">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="E254">
         <v>52</v>
@@ -11632,10 +11632,10 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>845</v>
+        <v>1282</v>
       </c>
       <c r="D255">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E255">
         <v>52</v>
@@ -11676,16 +11676,16 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>1692</v>
+        <v>1184</v>
       </c>
       <c r="D256">
-        <v>1210</v>
+        <v>2036</v>
       </c>
       <c r="E256">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F256">
-        <v>1661.9</v>
+        <v>2123.72</v>
       </c>
       <c r="G256">
         <v>0</v>
@@ -11706,10 +11706,10 @@
         <v>15</v>
       </c>
       <c r="M256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N256">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -11720,10 +11720,10 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>1455</v>
+        <v>842</v>
       </c>
       <c r="D257">
-        <v>2027</v>
+        <v>2045</v>
       </c>
       <c r="E257">
         <v>52</v>
@@ -11732,19 +11732,19 @@
         <v>2123.72</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H257">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I257">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J257">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="K257">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
@@ -11753,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="N257">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11829,10 +11829,10 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>1.6496</v>
+        <v>1.6846</v>
       </c>
       <c r="D2">
-        <v>7.3339</v>
+        <v>11.4043</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
